--- a/12608100.xlsx
+++ b/12608100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/178e7b8b65df52d4/Desktop/CAP-776/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="348" documentId="8_{423A2F30-43C3-4C4F-AB9B-22B4BC24882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A285848-CEBF-490D-A596-6369E561FB66}"/>
+  <xr:revisionPtr revIDLastSave="428" documentId="8_{423A2F30-43C3-4C4F-AB9B-22B4BC24882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{054C133E-AD16-49F6-A3CC-D8FDE99EFF10}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,21 @@
   </si>
   <si>
     <t>Today 2 CAs</t>
+  </si>
+  <si>
+    <t>exhausted</t>
+  </si>
+  <si>
+    <t>finally weekend</t>
+  </si>
+  <si>
+    <t>too much chores to do</t>
+  </si>
+  <si>
+    <t>homesickness and rain</t>
+  </si>
+  <si>
+    <t>good day and light feeling</t>
   </si>
 </sst>
 </file>
@@ -2376,169 +2391,323 @@
       <c r="A34" s="8">
         <v>46273</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="14" t="str">
+      <c r="B34" s="13">
+        <v>420</v>
+      </c>
+      <c r="C34" s="13">
+        <v>30</v>
+      </c>
+      <c r="D34" s="13">
+        <v>120</v>
+      </c>
+      <c r="E34" s="13">
+        <v>60</v>
+      </c>
+      <c r="F34" s="13">
+        <v>350</v>
+      </c>
+      <c r="G34" s="13">
+        <v>7</v>
+      </c>
+      <c r="H34" s="13">
+        <v>60</v>
+      </c>
+      <c r="I34" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="14" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J34" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="16"/>
+        <v>400</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="M34" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="16" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>46274</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="14" t="str">
+      <c r="B35" s="13">
+        <v>420</v>
+      </c>
+      <c r="C35" s="13">
+        <v>20</v>
+      </c>
+      <c r="D35" s="13">
+        <v>180</v>
+      </c>
+      <c r="E35" s="13">
+        <v>0</v>
+      </c>
+      <c r="F35" s="13">
+        <v>200</v>
+      </c>
+      <c r="G35" s="13">
+        <v>4</v>
+      </c>
+      <c r="H35" s="13">
+        <v>120</v>
+      </c>
+      <c r="I35" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="14" t="str">
+        <v>940</v>
+      </c>
+      <c r="J35" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N35" s="16" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>46275</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="14" t="str">
+      <c r="B36" s="13">
+        <v>360</v>
+      </c>
+      <c r="C36" s="13">
+        <v>20</v>
+      </c>
+      <c r="D36" s="13">
+        <v>60</v>
+      </c>
+      <c r="E36" s="13">
+        <v>45</v>
+      </c>
+      <c r="F36" s="13">
+        <v>350</v>
+      </c>
+      <c r="G36" s="13">
+        <v>7</v>
+      </c>
+      <c r="H36" s="13">
+        <v>150</v>
+      </c>
+      <c r="I36" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="14" t="str">
+        <v>985</v>
+      </c>
+      <c r="J36" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="16"/>
+        <v>455</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N36" s="16" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>46276</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="14" t="str">
+      <c r="B37" s="13">
+        <v>480</v>
+      </c>
+      <c r="C37" s="13">
+        <v>20</v>
+      </c>
+      <c r="D37" s="13">
+        <v>120</v>
+      </c>
+      <c r="E37" s="13">
+        <v>60</v>
+      </c>
+      <c r="F37" s="13">
+        <v>300</v>
+      </c>
+      <c r="G37" s="13">
+        <v>6</v>
+      </c>
+      <c r="H37" s="13">
+        <v>60</v>
+      </c>
+      <c r="I37" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="14" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J37" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="16"/>
+        <v>400</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="16" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>46277</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="14" t="str">
+      <c r="B38" s="13">
+        <v>540</v>
+      </c>
+      <c r="C38" s="13">
+        <v>30</v>
+      </c>
+      <c r="D38" s="13">
+        <v>150</v>
+      </c>
+      <c r="E38" s="13">
+        <v>120</v>
+      </c>
+      <c r="F38" s="13">
+        <v>0</v>
+      </c>
+      <c r="G38" s="13">
+        <v>0</v>
+      </c>
+      <c r="H38" s="13">
+        <v>180</v>
+      </c>
+      <c r="I38" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="14" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J38" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K38" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="L38" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="M38" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N38" s="16" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>46278</v>
       </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="14" t="str">
+      <c r="B39" s="13">
+        <v>600</v>
+      </c>
+      <c r="C39" s="13">
+        <v>25</v>
+      </c>
+      <c r="D39" s="13">
+        <v>180</v>
+      </c>
+      <c r="E39" s="13">
+        <v>60</v>
+      </c>
+      <c r="F39" s="13">
+        <v>0</v>
+      </c>
+      <c r="G39" s="13">
+        <v>0</v>
+      </c>
+      <c r="H39" s="13">
+        <v>180</v>
+      </c>
+      <c r="I39" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="14" t="str">
+        <v>1045</v>
+      </c>
+      <c r="J39" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="16"/>
+        <v>395</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L39" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M39" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="16" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>46279</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="14" t="str">
+      <c r="B40" s="13">
+        <v>360</v>
+      </c>
+      <c r="C40" s="13">
+        <v>20</v>
+      </c>
+      <c r="D40" s="13">
+        <v>120</v>
+      </c>
+      <c r="E40" s="13">
+        <v>30</v>
+      </c>
+      <c r="F40" s="13">
+        <v>150</v>
+      </c>
+      <c r="G40" s="13">
+        <v>3</v>
+      </c>
+      <c r="H40" s="13">
+        <v>120</v>
+      </c>
+      <c r="I40" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="14" t="str">
+        <v>800</v>
+      </c>
+      <c r="J40" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="16"/>
+        <v>640</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L40" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="M40" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N40" s="16" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="8">

--- a/12608100.xlsx
+++ b/12608100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/178e7b8b65df52d4/Desktop/CAP-776/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="428" documentId="8_{423A2F30-43C3-4C4F-AB9B-22B4BC24882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{054C133E-AD16-49F6-A3CC-D8FDE99EFF10}"/>
+  <xr:revisionPtr revIDLastSave="451" documentId="8_{423A2F30-43C3-4C4F-AB9B-22B4BC24882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69340C58-F1FC-406C-822A-B84EBCD66AF6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -317,6 +317,12 @@
   </si>
   <si>
     <t>good day and light feeling</t>
+  </si>
+  <si>
+    <t>python first ca completed</t>
+  </si>
+  <si>
+    <t>started something new</t>
   </si>
 </sst>
 </file>
@@ -2713,49 +2719,93 @@
       <c r="A41" s="8">
         <v>46280</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="14" t="str">
+      <c r="B41" s="13">
+        <v>420</v>
+      </c>
+      <c r="C41" s="13">
+        <v>25</v>
+      </c>
+      <c r="D41" s="13">
+        <v>60</v>
+      </c>
+      <c r="E41" s="13">
+        <v>60</v>
+      </c>
+      <c r="F41" s="13">
+        <v>250</v>
+      </c>
+      <c r="G41" s="13">
+        <v>5</v>
+      </c>
+      <c r="H41" s="13">
+        <v>120</v>
+      </c>
+      <c r="I41" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="14" t="str">
+        <v>935</v>
+      </c>
+      <c r="J41" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
-      <c r="N41" s="16"/>
+        <v>505</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="M41" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N41" s="16" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>46281</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="14" t="str">
+      <c r="B42" s="13">
+        <v>390</v>
+      </c>
+      <c r="C42" s="13">
+        <v>30</v>
+      </c>
+      <c r="D42" s="13">
+        <v>240</v>
+      </c>
+      <c r="E42" s="13">
+        <v>30</v>
+      </c>
+      <c r="F42" s="13">
+        <v>150</v>
+      </c>
+      <c r="G42" s="13">
+        <v>3</v>
+      </c>
+      <c r="H42" s="13">
+        <v>180</v>
+      </c>
+      <c r="I42" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="14" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J42" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
-      <c r="N42" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M42" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="16" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="8">

--- a/12608100.xlsx
+++ b/12608100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/178e7b8b65df52d4/Desktop/CAP-776/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="451" documentId="8_{423A2F30-43C3-4C4F-AB9B-22B4BC24882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69340C58-F1FC-406C-822A-B84EBCD66AF6}"/>
+  <xr:revisionPtr revIDLastSave="463" documentId="8_{423A2F30-43C3-4C4F-AB9B-22B4BC24882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0878A70-6C23-45CB-BC1E-6B67F6D571B1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>started something new</t>
+  </si>
+  <si>
+    <t>a day went right</t>
   </si>
 </sst>
 </file>
@@ -2811,25 +2814,47 @@
       <c r="A43" s="8">
         <v>46282</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="14" t="str">
+      <c r="B43" s="13">
+        <v>480</v>
+      </c>
+      <c r="C43" s="13">
+        <v>40</v>
+      </c>
+      <c r="D43" s="13">
+        <v>120</v>
+      </c>
+      <c r="E43" s="13">
+        <v>60</v>
+      </c>
+      <c r="F43" s="13">
+        <v>350</v>
+      </c>
+      <c r="G43" s="13">
+        <v>7</v>
+      </c>
+      <c r="H43" s="13">
+        <v>120</v>
+      </c>
+      <c r="I43" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="14" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J43" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="15"/>
-      <c r="N43" s="16"/>
+        <v>270</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="8">

--- a/12608100.xlsx
+++ b/12608100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/178e7b8b65df52d4/Desktop/CAP-776/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="463" documentId="8_{423A2F30-43C3-4C4F-AB9B-22B4BC24882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0878A70-6C23-45CB-BC1E-6B67F6D571B1}"/>
+  <xr:revisionPtr revIDLastSave="599" documentId="8_{423A2F30-43C3-4C4F-AB9B-22B4BC24882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F421DB10-78C9-4A38-A019-39D197CAB668}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -327,6 +327,30 @@
   <si>
     <t>a day went right</t>
   </si>
+  <si>
+    <t xml:space="preserve">ok </t>
+  </si>
+  <si>
+    <t>it's Saturday. My mom has came to meet me</t>
+  </si>
+  <si>
+    <t>happy weekend</t>
+  </si>
+  <si>
+    <t>train was too late..tired</t>
+  </si>
+  <si>
+    <t>fine</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>it's a good day</t>
+  </si>
+  <si>
+    <t>dbms ca went fine</t>
+  </si>
 </sst>
 </file>
 
@@ -335,7 +359,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -416,6 +440,35 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF5F5F5F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF5F5F5F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF5F5F5F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -464,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -507,6 +560,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -594,6 +665,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FF5F5F5F"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -980,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N402"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -1157,48 +1231,48 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="21">
         <v>46246</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="22">
         <v>420</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="23">
         <v>35</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="23">
         <v>60</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="23">
         <v>30</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="23">
         <v>200</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="23">
         <v>4</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="23">
         <v>120</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="24">
         <f t="shared" si="0"/>
         <v>865</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="24">
         <f t="shared" si="1"/>
         <v>575</v>
       </c>
-      <c r="K7" s="15" t="s">
+      <c r="K7" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="M7" s="15" t="s">
+      <c r="M7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="26" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1206,45 +1280,45 @@
       <c r="A8" s="8">
         <v>46247</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="23">
         <v>350</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="23">
         <v>30</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="23">
         <v>75</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="23">
         <v>45</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="23">
         <v>400</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="23">
         <v>8</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="23">
         <v>180</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="24">
         <f t="shared" si="0"/>
         <v>1080</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="24">
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="M8" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="N8" s="16" t="s">
+      <c r="N8" s="26" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1252,45 +1326,45 @@
       <c r="A9" s="8">
         <v>46248</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="23">
         <v>420</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="23">
         <v>20</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="23">
         <v>90</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="23">
         <v>60</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="23">
         <v>350</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="23">
         <v>7</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="23">
         <v>150</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="24">
         <f t="shared" si="0"/>
         <v>1090</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="24">
         <f t="shared" si="1"/>
         <v>350</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="M9" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="16" t="s">
+      <c r="N9" s="26" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1298,45 +1372,45 @@
       <c r="A10" s="8">
         <v>46249</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="23">
         <v>650</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="23">
         <v>40</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="23">
         <v>60</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="23">
         <v>40</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="23">
         <v>0</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="23">
         <v>0</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="23">
         <v>120</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="24">
         <f t="shared" si="0"/>
         <v>910</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="24">
         <f t="shared" si="1"/>
         <v>530</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="K10" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="L10" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="15" t="s">
+      <c r="M10" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="16" t="s">
+      <c r="N10" s="26" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1344,45 +1418,45 @@
       <c r="A11" s="8">
         <v>46250</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="23">
         <v>660</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="23">
         <v>0</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="23">
         <v>120</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="23">
         <v>0</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="23">
         <v>0</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="23">
         <v>0</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="23">
         <v>60</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="24">
         <f t="shared" si="0"/>
         <v>840</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="24">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="K11" s="15" t="s">
+      <c r="K11" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="M11" s="15" t="s">
+      <c r="M11" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="N11" s="26" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1390,45 +1464,45 @@
       <c r="A12" s="8">
         <v>46251</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="23">
         <v>600</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="23">
         <v>15</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="23">
         <v>30</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="23">
         <v>60</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="23">
         <v>0</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="23">
         <v>0</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="23">
         <v>180</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="24">
         <f t="shared" si="0"/>
         <v>885</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="24">
         <f t="shared" si="1"/>
         <v>555</v>
       </c>
-      <c r="K12" s="15" t="s">
+      <c r="K12" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="L12" s="15" t="s">
+      <c r="L12" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M12" s="15" t="s">
+      <c r="M12" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="N12" s="16" t="s">
+      <c r="N12" s="26" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1436,45 +1510,45 @@
       <c r="A13" s="8">
         <v>46252</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="23">
         <v>300</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="23">
         <v>30</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="23">
         <v>120</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="23">
         <v>120</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="23">
         <v>400</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="23">
         <v>8</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="23">
         <v>90</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="24">
         <f t="shared" si="0"/>
         <v>1060</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="24">
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="K13" s="15" t="s">
+      <c r="K13" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="L13" s="15" t="s">
+      <c r="L13" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M13" s="15" t="s">
+      <c r="M13" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N13" s="16" t="s">
+      <c r="N13" s="26" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1482,89 +1556,89 @@
       <c r="A14" s="8">
         <v>46253</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="23">
         <v>420</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="23">
         <v>30</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="23">
         <v>120</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="23">
         <v>60</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="23">
         <v>200</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="23">
         <v>4</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="23">
         <v>60</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="24">
         <f t="shared" si="0"/>
         <v>890</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="24">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
-      <c r="K14" s="15" t="s">
+      <c r="K14" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="15" t="s">
+      <c r="L14" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="15" t="s">
+      <c r="M14" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="16"/>
+      <c r="N14" s="26"/>
     </row>
     <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>46254</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="23">
         <v>420</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="23">
         <v>20</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="23">
         <v>60</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="23">
         <v>45</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="23">
         <v>400</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="23">
         <v>8</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="23">
         <v>180</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="24">
         <f t="shared" si="0"/>
         <v>1125</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="24">
         <f t="shared" si="1"/>
         <v>315</v>
       </c>
-      <c r="K15" s="15" t="s">
+      <c r="K15" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="L15" s="15" t="s">
+      <c r="L15" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M15" s="15" t="s">
+      <c r="M15" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="N15" s="16" t="s">
+      <c r="N15" s="26" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1572,45 +1646,45 @@
       <c r="A16" s="8">
         <v>46255</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="23">
         <v>480</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="23">
         <v>15</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="23">
         <v>45</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="23">
         <v>120</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="23">
         <v>300</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="23">
         <v>6</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="23">
         <v>150</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="24">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="24">
         <f t="shared" si="1"/>
         <v>330</v>
       </c>
-      <c r="K16" s="15" t="s">
+      <c r="K16" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="L16" s="15" t="s">
+      <c r="L16" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M16" s="15" t="s">
+      <c r="M16" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N16" s="16" t="s">
+      <c r="N16" s="26" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1618,45 +1692,45 @@
       <c r="A17" s="8">
         <v>46256</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="23">
         <v>720</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="23">
         <v>20</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="23">
         <v>30</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="23">
         <v>0</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="23">
         <v>0</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="23">
         <v>0</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="23">
         <v>120</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="24">
         <f t="shared" si="0"/>
         <v>890</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="24">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
-      <c r="K17" s="15" t="s">
+      <c r="K17" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="L17" s="15" t="s">
+      <c r="L17" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="15" t="s">
+      <c r="M17" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="N17" s="16" t="s">
+      <c r="N17" s="26" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1664,45 +1738,45 @@
       <c r="A18" s="8">
         <v>46257</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="23">
         <v>840</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="23">
         <v>0</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="23">
         <v>60</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="23">
         <v>60</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="23">
         <v>0</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="23">
         <v>0</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="23">
         <v>60</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="24">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="24">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="K18" s="15" t="s">
+      <c r="K18" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="L18" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="M18" s="15" t="s">
+      <c r="M18" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="N18" s="16" t="s">
+      <c r="N18" s="26" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1710,45 +1784,45 @@
       <c r="A19" s="8">
         <v>46258</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="23">
         <v>480</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="23">
         <v>40</v>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="23">
         <v>60</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="23">
         <v>30</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="23">
         <v>200</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="23">
         <v>4</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="23">
         <v>120</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="24">
         <f t="shared" si="0"/>
         <v>930</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="24">
         <f t="shared" si="1"/>
         <v>510</v>
       </c>
-      <c r="K19" s="15" t="s">
+      <c r="K19" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="L19" s="15" t="s">
+      <c r="L19" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M19" s="15" t="s">
+      <c r="M19" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N19" s="16" t="s">
+      <c r="N19" s="26" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1756,45 +1830,45 @@
       <c r="A20" s="8">
         <v>46259</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="23">
         <v>480</v>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="23">
         <v>20</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="23">
         <v>120</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="23">
         <v>60</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="23">
         <v>350</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="23">
         <v>7</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="23">
         <v>90</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="24">
         <f t="shared" si="0"/>
         <v>1120</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="24">
         <f t="shared" si="1"/>
         <v>320</v>
       </c>
-      <c r="K20" s="15" t="s">
+      <c r="K20" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L20" s="15" t="s">
+      <c r="L20" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M20" s="15" t="s">
+      <c r="M20" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N20" s="16" t="s">
+      <c r="N20" s="26" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1802,45 +1876,45 @@
       <c r="A21" s="8">
         <v>46260</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="23">
         <v>350</v>
       </c>
-      <c r="C21" s="13">
+      <c r="C21" s="23">
         <v>30</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="23">
         <v>60</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="23">
         <v>120</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="23">
         <v>200</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="23">
         <v>4</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="23">
         <v>120</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="24">
         <f t="shared" si="0"/>
         <v>880</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="24">
         <f t="shared" si="1"/>
         <v>560</v>
       </c>
-      <c r="K21" s="15" t="s">
+      <c r="K21" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L21" s="15" t="s">
+      <c r="L21" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M21" s="15" t="s">
+      <c r="M21" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N21" s="16" t="s">
+      <c r="N21" s="26" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1848,45 +1922,45 @@
       <c r="A22" s="8">
         <v>46261</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="23">
         <v>420</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="23">
         <v>40</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="23">
         <v>30</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="23">
         <v>30</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="23">
         <v>350</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="23">
         <v>7</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="23">
         <v>60</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="24">
         <f t="shared" si="0"/>
         <v>930</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="24">
         <f t="shared" si="1"/>
         <v>510</v>
       </c>
-      <c r="K22" s="15" t="s">
+      <c r="K22" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="L22" s="15" t="s">
+      <c r="L22" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M22" s="15" t="s">
+      <c r="M22" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="N22" s="16" t="s">
+      <c r="N22" s="26" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1894,45 +1968,45 @@
       <c r="A23" s="8">
         <v>46262</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="23">
         <v>480</v>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="23">
         <v>20</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="23">
         <v>120</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="23">
         <v>60</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="23">
         <v>100</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="23">
         <v>2</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="23">
         <v>180</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="24">
         <f t="shared" si="0"/>
         <v>960</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="24">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="K23" s="15" t="s">
+      <c r="K23" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="L23" s="15" t="s">
+      <c r="L23" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M23" s="15" t="s">
+      <c r="M23" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N23" s="16" t="s">
+      <c r="N23" s="26" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1940,45 +2014,45 @@
       <c r="A24" s="8">
         <v>46263</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="23">
         <v>540</v>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="23">
         <v>20</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="23">
         <v>180</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="23">
         <v>0</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="23">
         <v>0</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="23">
         <v>0</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="23">
         <v>120</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="24">
         <f t="shared" si="0"/>
         <v>860</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="24">
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
-      <c r="K24" s="15" t="s">
+      <c r="K24" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="L24" s="15" t="s">
+      <c r="L24" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="M24" s="15" t="s">
+      <c r="M24" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N24" s="16" t="s">
+      <c r="N24" s="26" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1986,45 +2060,45 @@
       <c r="A25" s="8">
         <v>46264</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="23">
         <v>600</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C25" s="23">
         <v>20</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="23">
         <v>120</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="23">
         <v>120</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="23">
         <v>0</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="23">
         <v>0</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="23">
         <v>180</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="24">
         <f t="shared" si="0"/>
         <v>1040</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="24">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
-      <c r="K25" s="15" t="s">
+      <c r="K25" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L25" s="15" t="s">
+      <c r="L25" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M25" s="15" t="s">
+      <c r="M25" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N25" s="16" t="s">
+      <c r="N25" s="26" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2032,45 +2106,45 @@
       <c r="A26" s="8">
         <v>46265</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="23">
         <v>540</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="23">
         <v>30</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="23">
         <v>60</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="23">
         <v>60</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="23">
         <v>100</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="23">
         <v>2</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="23">
         <v>120</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="24">
         <f t="shared" si="0"/>
         <v>910</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="24">
         <f t="shared" si="1"/>
         <v>530</v>
       </c>
-      <c r="K26" s="15" t="s">
+      <c r="K26" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="L26" s="15" t="s">
+      <c r="L26" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M26" s="15" t="s">
+      <c r="M26" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="16" t="s">
+      <c r="N26" s="26" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2078,45 +2152,45 @@
       <c r="A27" s="8">
         <v>46266</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="23">
         <v>420</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="23">
         <v>30</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="23">
         <v>60</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="23">
         <v>30</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="23">
         <v>200</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="23">
         <v>4</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="23">
         <v>120</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="24">
         <f t="shared" si="0"/>
         <v>860</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="24">
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
-      <c r="K27" s="15" t="s">
+      <c r="K27" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="L27" s="15" t="s">
+      <c r="L27" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M27" s="15" t="s">
+      <c r="M27" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N27" s="16" t="s">
+      <c r="N27" s="26" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2124,45 +2198,45 @@
       <c r="A28" s="8">
         <v>46267</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="23">
         <v>420</v>
       </c>
-      <c r="C28" s="13">
+      <c r="C28" s="23">
         <v>15</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="23">
         <v>120</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="23">
         <v>60</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="23">
         <v>200</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="23">
         <v>4</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="23">
         <v>60</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="24">
         <f t="shared" si="0"/>
         <v>875</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="24">
         <f t="shared" si="1"/>
         <v>565</v>
       </c>
-      <c r="K28" s="15" t="s">
+      <c r="K28" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="L28" s="15" t="s">
+      <c r="L28" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="M28" s="15" t="s">
+      <c r="M28" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="N28" s="16" t="s">
+      <c r="N28" s="26" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2170,45 +2244,45 @@
       <c r="A29" s="8">
         <v>46268</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="23">
         <v>480</v>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="23">
         <v>25</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="23">
         <v>60</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="23">
         <v>60</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="23">
         <v>350</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="23">
         <v>7</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="23">
         <v>150</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="24">
         <f t="shared" si="0"/>
         <v>1125</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="24">
         <f t="shared" si="1"/>
         <v>315</v>
       </c>
-      <c r="K29" s="15" t="s">
+      <c r="K29" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="L29" s="15" t="s">
+      <c r="L29" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M29" s="15" t="s">
+      <c r="M29" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="N29" s="16" t="s">
+      <c r="N29" s="26" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2216,45 +2290,45 @@
       <c r="A30" s="8">
         <v>46269</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="23">
         <v>360</v>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="23">
         <v>30</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="23">
         <v>30</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="23">
         <v>120</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="23">
         <v>300</v>
       </c>
-      <c r="G30" s="13">
+      <c r="G30" s="23">
         <v>6</v>
       </c>
-      <c r="H30" s="13">
+      <c r="H30" s="23">
         <v>180</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="24">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="24">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="K30" s="15" t="s">
+      <c r="K30" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L30" s="15" t="s">
+      <c r="L30" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M30" s="15" t="s">
+      <c r="M30" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N30" s="16" t="s">
+      <c r="N30" s="26" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2262,45 +2336,45 @@
       <c r="A31" s="8">
         <v>46270</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="23">
         <v>540</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="23">
         <v>0</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="23">
         <v>120</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="23">
         <v>60</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="23">
         <v>0</v>
       </c>
-      <c r="G31" s="13">
+      <c r="G31" s="23">
         <v>0</v>
       </c>
-      <c r="H31" s="13">
+      <c r="H31" s="23">
         <v>120</v>
       </c>
-      <c r="I31" s="14">
+      <c r="I31" s="24">
         <f t="shared" si="0"/>
         <v>840</v>
       </c>
-      <c r="J31" s="14">
+      <c r="J31" s="24">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="K31" s="15" t="s">
+      <c r="K31" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L31" s="15" t="s">
+      <c r="L31" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M31" s="15" t="s">
+      <c r="M31" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="N31" s="16" t="s">
+      <c r="N31" s="26" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2308,45 +2382,45 @@
       <c r="A32" s="8">
         <v>46271</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="23">
         <v>540</v>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="23">
         <v>20</v>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="23">
         <v>180</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="23">
         <v>30</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="23">
         <v>0</v>
       </c>
-      <c r="G32" s="13">
+      <c r="G32" s="23">
         <v>0</v>
       </c>
-      <c r="H32" s="13">
+      <c r="H32" s="23">
         <v>120</v>
       </c>
-      <c r="I32" s="14">
+      <c r="I32" s="24">
         <f t="shared" si="0"/>
         <v>890</v>
       </c>
-      <c r="J32" s="14">
+      <c r="J32" s="24">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
-      <c r="K32" s="15" t="s">
+      <c r="K32" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="L32" s="15" t="s">
+      <c r="L32" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="M32" s="15" t="s">
+      <c r="M32" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N32" s="16" t="s">
+      <c r="N32" s="26" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2354,45 +2428,45 @@
       <c r="A33" s="8">
         <v>46272</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="23">
         <v>420</v>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="23">
         <v>30</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="23">
         <v>210</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="23">
         <v>30</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="23">
         <v>200</v>
       </c>
-      <c r="G33" s="13">
+      <c r="G33" s="23">
         <v>4</v>
       </c>
-      <c r="H33" s="13">
+      <c r="H33" s="23">
         <v>90</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="24">
         <f t="shared" si="0"/>
         <v>980</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="24">
         <f t="shared" si="1"/>
         <v>460</v>
       </c>
-      <c r="K33" s="15" t="s">
+      <c r="K33" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L33" s="15" t="s">
+      <c r="L33" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M33" s="15" t="s">
+      <c r="M33" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N33" s="16" t="s">
+      <c r="N33" s="26" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2400,45 +2474,45 @@
       <c r="A34" s="8">
         <v>46273</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="23">
         <v>420</v>
       </c>
-      <c r="C34" s="13">
+      <c r="C34" s="23">
         <v>30</v>
       </c>
-      <c r="D34" s="13">
+      <c r="D34" s="23">
         <v>120</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="23">
         <v>60</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="23">
         <v>350</v>
       </c>
-      <c r="G34" s="13">
+      <c r="G34" s="23">
         <v>7</v>
       </c>
-      <c r="H34" s="13">
+      <c r="H34" s="23">
         <v>60</v>
       </c>
-      <c r="I34" s="14">
+      <c r="I34" s="24">
         <f t="shared" si="0"/>
         <v>1040</v>
       </c>
-      <c r="J34" s="14">
+      <c r="J34" s="24">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
-      <c r="K34" s="15" t="s">
+      <c r="K34" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L34" s="15" t="s">
+      <c r="L34" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M34" s="15" t="s">
+      <c r="M34" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N34" s="16" t="s">
+      <c r="N34" s="26" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2446,45 +2520,45 @@
       <c r="A35" s="8">
         <v>46274</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="23">
         <v>420</v>
       </c>
-      <c r="C35" s="13">
+      <c r="C35" s="23">
         <v>20</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="23">
         <v>180</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="23">
         <v>0</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="23">
         <v>200</v>
       </c>
-      <c r="G35" s="13">
+      <c r="G35" s="23">
         <v>4</v>
       </c>
-      <c r="H35" s="13">
+      <c r="H35" s="23">
         <v>120</v>
       </c>
-      <c r="I35" s="14">
+      <c r="I35" s="24">
         <f t="shared" si="0"/>
         <v>940</v>
       </c>
-      <c r="J35" s="14">
+      <c r="J35" s="24">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="K35" s="15" t="s">
+      <c r="K35" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="L35" s="15" t="s">
+      <c r="L35" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M35" s="15" t="s">
+      <c r="M35" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="N35" s="16" t="s">
+      <c r="N35" s="26" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2492,45 +2566,45 @@
       <c r="A36" s="8">
         <v>46275</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="23">
         <v>360</v>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="23">
         <v>20</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="23">
         <v>60</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="23">
         <v>45</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="23">
         <v>350</v>
       </c>
-      <c r="G36" s="13">
+      <c r="G36" s="23">
         <v>7</v>
       </c>
-      <c r="H36" s="13">
+      <c r="H36" s="23">
         <v>150</v>
       </c>
-      <c r="I36" s="14">
+      <c r="I36" s="24">
         <f t="shared" si="0"/>
         <v>985</v>
       </c>
-      <c r="J36" s="14">
+      <c r="J36" s="24">
         <f t="shared" si="1"/>
         <v>455</v>
       </c>
-      <c r="K36" s="15" t="s">
+      <c r="K36" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="L36" s="15" t="s">
+      <c r="L36" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M36" s="15" t="s">
+      <c r="M36" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="N36" s="16" t="s">
+      <c r="N36" s="26" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2538,45 +2612,45 @@
       <c r="A37" s="8">
         <v>46276</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="23">
         <v>480</v>
       </c>
-      <c r="C37" s="13">
+      <c r="C37" s="23">
         <v>20</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="23">
         <v>120</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="23">
         <v>60</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="23">
         <v>300</v>
       </c>
-      <c r="G37" s="13">
+      <c r="G37" s="23">
         <v>6</v>
       </c>
-      <c r="H37" s="13">
+      <c r="H37" s="23">
         <v>60</v>
       </c>
-      <c r="I37" s="14">
+      <c r="I37" s="24">
         <f t="shared" si="0"/>
         <v>1040</v>
       </c>
-      <c r="J37" s="14">
+      <c r="J37" s="24">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
-      <c r="K37" s="15" t="s">
+      <c r="K37" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="L37" s="15" t="s">
+      <c r="L37" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M37" s="15" t="s">
+      <c r="M37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N37" s="16" t="s">
+      <c r="N37" s="26" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2584,45 +2658,45 @@
       <c r="A38" s="8">
         <v>46277</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="23">
         <v>540</v>
       </c>
-      <c r="C38" s="13">
+      <c r="C38" s="23">
         <v>30</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="23">
         <v>150</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="23">
         <v>120</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="23">
         <v>0</v>
       </c>
-      <c r="G38" s="13">
+      <c r="G38" s="23">
         <v>0</v>
       </c>
-      <c r="H38" s="13">
+      <c r="H38" s="23">
         <v>180</v>
       </c>
-      <c r="I38" s="14">
+      <c r="I38" s="24">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
-      <c r="J38" s="14">
+      <c r="J38" s="24">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="K38" s="15" t="s">
+      <c r="K38" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="L38" s="15" t="s">
+      <c r="L38" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="M38" s="15" t="s">
+      <c r="M38" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="N38" s="16" t="s">
+      <c r="N38" s="26" t="s">
         <v>91</v>
       </c>
     </row>
@@ -2630,45 +2704,45 @@
       <c r="A39" s="8">
         <v>46278</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="23">
         <v>600</v>
       </c>
-      <c r="C39" s="13">
+      <c r="C39" s="23">
         <v>25</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="23">
         <v>180</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="23">
         <v>60</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="23">
         <v>0</v>
       </c>
-      <c r="G39" s="13">
+      <c r="G39" s="23">
         <v>0</v>
       </c>
-      <c r="H39" s="13">
+      <c r="H39" s="23">
         <v>180</v>
       </c>
-      <c r="I39" s="14">
+      <c r="I39" s="24">
         <f t="shared" si="0"/>
         <v>1045</v>
       </c>
-      <c r="J39" s="14">
+      <c r="J39" s="24">
         <f t="shared" si="1"/>
         <v>395</v>
       </c>
-      <c r="K39" s="15" t="s">
+      <c r="K39" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="L39" s="15" t="s">
+      <c r="L39" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="M39" s="15" t="s">
+      <c r="M39" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N39" s="16" t="s">
+      <c r="N39" s="26" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2676,45 +2750,45 @@
       <c r="A40" s="8">
         <v>46279</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="23">
         <v>360</v>
       </c>
-      <c r="C40" s="13">
+      <c r="C40" s="23">
         <v>20</v>
       </c>
-      <c r="D40" s="13">
+      <c r="D40" s="23">
         <v>120</v>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="23">
         <v>30</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="23">
         <v>150</v>
       </c>
-      <c r="G40" s="13">
+      <c r="G40" s="23">
         <v>3</v>
       </c>
-      <c r="H40" s="13">
+      <c r="H40" s="23">
         <v>120</v>
       </c>
-      <c r="I40" s="14">
+      <c r="I40" s="24">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="J40" s="14">
+      <c r="J40" s="24">
         <f t="shared" si="1"/>
         <v>640</v>
       </c>
-      <c r="K40" s="15" t="s">
+      <c r="K40" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="L40" s="15" t="s">
+      <c r="L40" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M40" s="15" t="s">
+      <c r="M40" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="N40" s="16" t="s">
+      <c r="N40" s="26" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2722,45 +2796,45 @@
       <c r="A41" s="8">
         <v>46280</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="23">
         <v>420</v>
       </c>
-      <c r="C41" s="13">
+      <c r="C41" s="23">
         <v>25</v>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="23">
         <v>60</v>
       </c>
-      <c r="E41" s="13">
+      <c r="E41" s="23">
         <v>60</v>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="23">
         <v>250</v>
       </c>
-      <c r="G41" s="13">
+      <c r="G41" s="23">
         <v>5</v>
       </c>
-      <c r="H41" s="13">
+      <c r="H41" s="23">
         <v>120</v>
       </c>
-      <c r="I41" s="14">
+      <c r="I41" s="24">
         <f t="shared" si="0"/>
         <v>935</v>
       </c>
-      <c r="J41" s="14">
+      <c r="J41" s="24">
         <f t="shared" si="1"/>
         <v>505</v>
       </c>
-      <c r="K41" s="15" t="s">
+      <c r="K41" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="L41" s="15" t="s">
+      <c r="L41" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M41" s="15" t="s">
+      <c r="M41" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="N41" s="16" t="s">
+      <c r="N41" s="26" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2768,45 +2842,45 @@
       <c r="A42" s="8">
         <v>46281</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="23">
         <v>390</v>
       </c>
-      <c r="C42" s="13">
+      <c r="C42" s="23">
         <v>30</v>
       </c>
-      <c r="D42" s="13">
+      <c r="D42" s="23">
         <v>240</v>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="23">
         <v>30</v>
       </c>
-      <c r="F42" s="13">
+      <c r="F42" s="23">
         <v>150</v>
       </c>
-      <c r="G42" s="13">
+      <c r="G42" s="23">
         <v>3</v>
       </c>
-      <c r="H42" s="13">
+      <c r="H42" s="23">
         <v>180</v>
       </c>
-      <c r="I42" s="14">
+      <c r="I42" s="24">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
-      <c r="J42" s="14">
+      <c r="J42" s="24">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="K42" s="15" t="s">
+      <c r="K42" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L42" s="15" t="s">
+      <c r="L42" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="M42" s="15" t="s">
+      <c r="M42" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N42" s="16" t="s">
+      <c r="N42" s="26" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2814,45 +2888,45 @@
       <c r="A43" s="8">
         <v>46282</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="23">
         <v>480</v>
       </c>
-      <c r="C43" s="13">
+      <c r="C43" s="23">
         <v>40</v>
       </c>
-      <c r="D43" s="13">
+      <c r="D43" s="23">
         <v>120</v>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="23">
         <v>60</v>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="23">
         <v>350</v>
       </c>
-      <c r="G43" s="13">
+      <c r="G43" s="23">
         <v>7</v>
       </c>
-      <c r="H43" s="13">
+      <c r="H43" s="23">
         <v>120</v>
       </c>
-      <c r="I43" s="14">
+      <c r="I43" s="24">
         <f t="shared" si="0"/>
         <v>1170</v>
       </c>
-      <c r="J43" s="14">
+      <c r="J43" s="24">
         <f t="shared" si="1"/>
         <v>270</v>
       </c>
-      <c r="K43" s="15" t="s">
+      <c r="K43" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L43" s="15" t="s">
+      <c r="L43" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M43" s="15" t="s">
+      <c r="M43" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N43" s="16" t="s">
+      <c r="N43" s="26" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2860,222 +2934,418 @@
       <c r="A44" s="8">
         <v>46283</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="14" t="str">
+      <c r="B44" s="23">
+        <v>420</v>
+      </c>
+      <c r="C44" s="23">
+        <v>20</v>
+      </c>
+      <c r="D44" s="23">
+        <v>60</v>
+      </c>
+      <c r="E44" s="23">
+        <v>60</v>
+      </c>
+      <c r="F44" s="23">
+        <v>300</v>
+      </c>
+      <c r="G44" s="23">
+        <v>6</v>
+      </c>
+      <c r="H44" s="23">
+        <v>120</v>
+      </c>
+      <c r="I44" s="24">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="14" t="str">
+        <v>980</v>
+      </c>
+      <c r="J44" s="24">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="15"/>
-      <c r="N44" s="16"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+        <v>460</v>
+      </c>
+      <c r="K44" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="M44" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>46284</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="14" t="str">
+      <c r="B45" s="23">
+        <v>560</v>
+      </c>
+      <c r="C45" s="23">
+        <v>40</v>
+      </c>
+      <c r="D45" s="23">
+        <v>120</v>
+      </c>
+      <c r="E45" s="23">
+        <v>30</v>
+      </c>
+      <c r="F45" s="23">
+        <v>0</v>
+      </c>
+      <c r="G45" s="23">
+        <v>0</v>
+      </c>
+      <c r="H45" s="23">
+        <v>120</v>
+      </c>
+      <c r="I45" s="24">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="14" t="str">
+        <v>870</v>
+      </c>
+      <c r="J45" s="24">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K45" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="L45" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="N45" s="26" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>46285</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="14" t="str">
+      <c r="B46" s="23">
+        <v>620</v>
+      </c>
+      <c r="C46" s="23">
+        <v>20</v>
+      </c>
+      <c r="D46" s="23">
+        <v>180</v>
+      </c>
+      <c r="E46" s="23">
+        <v>60</v>
+      </c>
+      <c r="F46" s="23">
+        <v>0</v>
+      </c>
+      <c r="G46" s="23">
+        <v>0</v>
+      </c>
+      <c r="H46" s="23">
+        <v>180</v>
+      </c>
+      <c r="I46" s="24">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="14" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J46" s="24">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="16"/>
+        <v>380</v>
+      </c>
+      <c r="K46" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="L46" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="N46" s="26" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>46286</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="14" t="str">
+      <c r="B47" s="23">
+        <v>420</v>
+      </c>
+      <c r="C47" s="23">
+        <v>30</v>
+      </c>
+      <c r="D47" s="23">
+        <v>210</v>
+      </c>
+      <c r="E47" s="23">
+        <v>30</v>
+      </c>
+      <c r="F47" s="23">
+        <v>150</v>
+      </c>
+      <c r="G47" s="23">
+        <v>3</v>
+      </c>
+      <c r="H47" s="23">
+        <v>120</v>
+      </c>
+      <c r="I47" s="24">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="14" t="str">
+        <v>960</v>
+      </c>
+      <c r="J47" s="24">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
-      <c r="N47" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K47" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="L47" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="M47" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="26" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>46287</v>
       </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="14" t="str">
+      <c r="B48" s="23">
+        <v>480</v>
+      </c>
+      <c r="C48" s="23">
+        <v>20</v>
+      </c>
+      <c r="D48" s="23">
+        <v>60</v>
+      </c>
+      <c r="E48" s="23">
+        <v>30</v>
+      </c>
+      <c r="F48" s="23">
+        <v>350</v>
+      </c>
+      <c r="G48" s="23">
+        <v>7</v>
+      </c>
+      <c r="H48" s="23">
+        <v>60</v>
+      </c>
+      <c r="I48" s="24">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="14" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J48" s="24">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="16"/>
+        <v>440</v>
+      </c>
+      <c r="K48" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="M48" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="N48" s="26" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>46288</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="14" t="str">
+      <c r="B49" s="23">
+        <v>560</v>
+      </c>
+      <c r="C49" s="23">
+        <v>20</v>
+      </c>
+      <c r="D49" s="23">
+        <v>120</v>
+      </c>
+      <c r="E49" s="23">
+        <v>30</v>
+      </c>
+      <c r="F49" s="23">
+        <v>200</v>
+      </c>
+      <c r="G49" s="23">
+        <v>4</v>
+      </c>
+      <c r="H49" s="23">
+        <v>180</v>
+      </c>
+      <c r="I49" s="24">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="14" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J49" s="24">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
-      <c r="N49" s="16"/>
+        <v>330</v>
+      </c>
+      <c r="K49" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="L49" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="M49" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="26" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>46289</v>
       </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="14" t="str">
+      <c r="B50" s="23">
+        <v>420</v>
+      </c>
+      <c r="C50" s="23">
+        <v>25</v>
+      </c>
+      <c r="D50" s="23">
+        <v>60</v>
+      </c>
+      <c r="E50" s="23">
+        <v>60</v>
+      </c>
+      <c r="F50" s="23">
+        <v>350</v>
+      </c>
+      <c r="G50" s="23">
+        <v>7</v>
+      </c>
+      <c r="H50" s="23">
+        <v>150</v>
+      </c>
+      <c r="I50" s="24">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="14" t="str">
+        <v>1065</v>
+      </c>
+      <c r="J50" s="24">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="15"/>
-      <c r="L50" s="15"/>
-      <c r="M50" s="15"/>
-      <c r="N50" s="16"/>
+        <v>375</v>
+      </c>
+      <c r="K50" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="L50" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" s="26" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>46290</v>
       </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="14" t="str">
+      <c r="B51" s="23">
+        <v>420</v>
+      </c>
+      <c r="C51" s="23">
+        <v>30</v>
+      </c>
+      <c r="D51" s="23">
+        <v>60</v>
+      </c>
+      <c r="E51" s="23">
+        <v>120</v>
+      </c>
+      <c r="F51" s="23">
+        <v>300</v>
+      </c>
+      <c r="G51" s="23">
+        <v>6</v>
+      </c>
+      <c r="H51" s="23">
+        <v>120</v>
+      </c>
+      <c r="I51" s="24">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="14" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J51" s="24">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="15"/>
-      <c r="L51" s="15"/>
-      <c r="M51" s="15"/>
-      <c r="N51" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K51" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="26" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>46291</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="14" t="str">
+      <c r="B52" s="23">
+        <v>620</v>
+      </c>
+      <c r="C52" s="23">
+        <v>20</v>
+      </c>
+      <c r="D52" s="23">
+        <v>120</v>
+      </c>
+      <c r="E52" s="23">
+        <v>60</v>
+      </c>
+      <c r="F52" s="23">
+        <v>0</v>
+      </c>
+      <c r="G52" s="23">
+        <v>0</v>
+      </c>
+      <c r="H52" s="23">
+        <v>210</v>
+      </c>
+      <c r="I52" s="24">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="14" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J52" s="24">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="15"/>
-      <c r="N52" s="16"/>
+        <v>410</v>
+      </c>
+      <c r="K52" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="L52" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="M52" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="N52" s="26" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="8">
-        <v>46292</v>
-      </c>
+      <c r="A53" s="8"/>
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
@@ -3097,9 +3367,7 @@
       <c r="N53" s="16"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="8">
-        <v>46293</v>
-      </c>
+      <c r="A54" s="8"/>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
@@ -3121,9 +3389,7 @@
       <c r="N54" s="16"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="8">
-        <v>46294</v>
-      </c>
+      <c r="A55" s="8"/>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
@@ -3145,9 +3411,7 @@
       <c r="N55" s="16"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="8">
-        <v>46295</v>
-      </c>
+      <c r="A56" s="8"/>
       <c r="B56" s="13"/>
       <c r="C56" s="13"/>
       <c r="D56" s="13"/>
@@ -3169,9 +3433,7 @@
       <c r="N56" s="16"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="8">
-        <v>46296</v>
-      </c>
+      <c r="A57" s="8"/>
       <c r="B57" s="13"/>
       <c r="C57" s="13"/>
       <c r="D57" s="13"/>
@@ -3193,9 +3455,7 @@
       <c r="N57" s="16"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="8">
-        <v>46297</v>
-      </c>
+      <c r="A58" s="8"/>
       <c r="B58" s="13"/>
       <c r="C58" s="13"/>
       <c r="D58" s="13"/>
@@ -3217,9 +3477,7 @@
       <c r="N58" s="16"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="8">
-        <v>46298</v>
-      </c>
+      <c r="A59" s="8"/>
       <c r="B59" s="13"/>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
@@ -3241,9 +3499,7 @@
       <c r="N59" s="16"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="8">
-        <v>46299</v>
-      </c>
+      <c r="A60" s="8"/>
       <c r="B60" s="13"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
@@ -3265,9 +3521,7 @@
       <c r="N60" s="16"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="8">
-        <v>46300</v>
-      </c>
+      <c r="A61" s="8"/>
       <c r="B61" s="13"/>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
@@ -3289,9 +3543,7 @@
       <c r="N61" s="16"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="8">
-        <v>46301</v>
-      </c>
+      <c r="A62" s="8"/>
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
@@ -3313,9 +3565,7 @@
       <c r="N62" s="16"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="8">
-        <v>46302</v>
-      </c>
+      <c r="A63" s="8"/>
       <c r="B63" s="13"/>
       <c r="C63" s="13"/>
       <c r="D63" s="13"/>
@@ -3337,9 +3587,7 @@
       <c r="N63" s="16"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="8">
-        <v>46303</v>
-      </c>
+      <c r="A64" s="8"/>
       <c r="B64" s="13"/>
       <c r="C64" s="13"/>
       <c r="D64" s="13"/>
@@ -3361,9 +3609,7 @@
       <c r="N64" s="16"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="8">
-        <v>46304</v>
-      </c>
+      <c r="A65" s="8"/>
       <c r="B65" s="13"/>
       <c r="C65" s="13"/>
       <c r="D65" s="13"/>
@@ -3385,9 +3631,7 @@
       <c r="N65" s="16"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="8">
-        <v>46305</v>
-      </c>
+      <c r="A66" s="8"/>
       <c r="B66" s="13"/>
       <c r="C66" s="13"/>
       <c r="D66" s="13"/>
@@ -3409,9 +3653,7 @@
       <c r="N66" s="16"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="8">
-        <v>46306</v>
-      </c>
+      <c r="A67" s="8"/>
       <c r="B67" s="13"/>
       <c r="C67" s="13"/>
       <c r="D67" s="13"/>
@@ -3433,9 +3675,7 @@
       <c r="N67" s="16"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="8">
-        <v>46307</v>
-      </c>
+      <c r="A68" s="8"/>
       <c r="B68" s="13"/>
       <c r="C68" s="13"/>
       <c r="D68" s="13"/>
@@ -3457,9 +3697,7 @@
       <c r="N68" s="16"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="8">
-        <v>46308</v>
-      </c>
+      <c r="A69" s="8"/>
       <c r="B69" s="13"/>
       <c r="C69" s="13"/>
       <c r="D69" s="13"/>
@@ -3481,9 +3719,7 @@
       <c r="N69" s="16"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="8">
-        <v>46309</v>
-      </c>
+      <c r="A70" s="8"/>
       <c r="B70" s="13"/>
       <c r="C70" s="13"/>
       <c r="D70" s="13"/>
@@ -3505,9 +3741,7 @@
       <c r="N70" s="16"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="8">
-        <v>46310</v>
-      </c>
+      <c r="A71" s="8"/>
       <c r="B71" s="13"/>
       <c r="C71" s="13"/>
       <c r="D71" s="13"/>
@@ -3529,9 +3763,7 @@
       <c r="N71" s="16"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="8">
-        <v>46311</v>
-      </c>
+      <c r="A72" s="8"/>
       <c r="B72" s="13"/>
       <c r="C72" s="13"/>
       <c r="D72" s="13"/>
@@ -3553,9 +3785,7 @@
       <c r="N72" s="16"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="8">
-        <v>46312</v>
-      </c>
+      <c r="A73" s="8"/>
       <c r="B73" s="13"/>
       <c r="C73" s="13"/>
       <c r="D73" s="13"/>
@@ -3577,9 +3807,7 @@
       <c r="N73" s="16"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="8">
-        <v>46313</v>
-      </c>
+      <c r="A74" s="8"/>
       <c r="B74" s="13"/>
       <c r="C74" s="13"/>
       <c r="D74" s="13"/>
@@ -3601,9 +3829,7 @@
       <c r="N74" s="16"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="8">
-        <v>46314</v>
-      </c>
+      <c r="A75" s="8"/>
       <c r="B75" s="13"/>
       <c r="C75" s="13"/>
       <c r="D75" s="13"/>
@@ -3625,9 +3851,7 @@
       <c r="N75" s="16"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="8">
-        <v>46315</v>
-      </c>
+      <c r="A76" s="8"/>
       <c r="B76" s="13"/>
       <c r="C76" s="13"/>
       <c r="D76" s="13"/>
@@ -3649,9 +3873,7 @@
       <c r="N76" s="16"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="8">
-        <v>46316</v>
-      </c>
+      <c r="A77" s="8"/>
       <c r="B77" s="13"/>
       <c r="C77" s="13"/>
       <c r="D77" s="13"/>
@@ -3673,9 +3895,7 @@
       <c r="N77" s="16"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="8">
-        <v>46317</v>
-      </c>
+      <c r="A78" s="8"/>
       <c r="B78" s="13"/>
       <c r="C78" s="13"/>
       <c r="D78" s="13"/>
@@ -3697,9 +3917,7 @@
       <c r="N78" s="16"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="8">
-        <v>46318</v>
-      </c>
+      <c r="A79" s="8"/>
       <c r="B79" s="13"/>
       <c r="C79" s="13"/>
       <c r="D79" s="13"/>
@@ -3721,9 +3939,7 @@
       <c r="N79" s="16"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="8">
-        <v>46319</v>
-      </c>
+      <c r="A80" s="8"/>
       <c r="B80" s="13"/>
       <c r="C80" s="13"/>
       <c r="D80" s="13"/>
@@ -3745,9 +3961,7 @@
       <c r="N80" s="16"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="8">
-        <v>46320</v>
-      </c>
+      <c r="A81" s="8"/>
       <c r="B81" s="13"/>
       <c r="C81" s="13"/>
       <c r="D81" s="13"/>
@@ -3769,9 +3983,7 @@
       <c r="N81" s="16"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82" s="8">
-        <v>46321</v>
-      </c>
+      <c r="A82" s="8"/>
       <c r="B82" s="13"/>
       <c r="C82" s="13"/>
       <c r="D82" s="13"/>
@@ -3793,9 +4005,7 @@
       <c r="N82" s="16"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A83" s="8">
-        <v>46322</v>
-      </c>
+      <c r="A83" s="8"/>
       <c r="B83" s="13"/>
       <c r="C83" s="13"/>
       <c r="D83" s="13"/>
@@ -3817,9 +4027,7 @@
       <c r="N83" s="16"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A84" s="8">
-        <v>46323</v>
-      </c>
+      <c r="A84" s="8"/>
       <c r="B84" s="13"/>
       <c r="C84" s="13"/>
       <c r="D84" s="13"/>
@@ -3841,9 +4049,7 @@
       <c r="N84" s="16"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A85" s="8">
-        <v>46324</v>
-      </c>
+      <c r="A85" s="8"/>
       <c r="B85" s="13"/>
       <c r="C85" s="13"/>
       <c r="D85" s="13"/>
@@ -3865,9 +4071,7 @@
       <c r="N85" s="16"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A86" s="8">
-        <v>46325</v>
-      </c>
+      <c r="A86" s="8"/>
       <c r="B86" s="13"/>
       <c r="C86" s="13"/>
       <c r="D86" s="13"/>
@@ -3889,9 +4093,7 @@
       <c r="N86" s="16"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A87" s="8">
-        <v>46326</v>
-      </c>
+      <c r="A87" s="8"/>
       <c r="B87" s="13"/>
       <c r="C87" s="13"/>
       <c r="D87" s="13"/>
@@ -3913,9 +4115,7 @@
       <c r="N87" s="16"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A88" s="8">
-        <v>46327</v>
-      </c>
+      <c r="A88" s="8"/>
       <c r="B88" s="13"/>
       <c r="C88" s="13"/>
       <c r="D88" s="13"/>
@@ -3937,9 +4137,7 @@
       <c r="N88" s="16"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A89" s="8">
-        <v>46328</v>
-      </c>
+      <c r="A89" s="8"/>
       <c r="B89" s="13"/>
       <c r="C89" s="13"/>
       <c r="D89" s="13"/>
@@ -3961,9 +4159,7 @@
       <c r="N89" s="16"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A90" s="8">
-        <v>46329</v>
-      </c>
+      <c r="A90" s="8"/>
       <c r="B90" s="13"/>
       <c r="C90" s="13"/>
       <c r="D90" s="13"/>
@@ -3985,9 +4181,7 @@
       <c r="N90" s="16"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A91" s="8">
-        <v>46330</v>
-      </c>
+      <c r="A91" s="8"/>
       <c r="B91" s="13"/>
       <c r="C91" s="13"/>
       <c r="D91" s="13"/>
@@ -4009,9 +4203,7 @@
       <c r="N91" s="16"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A92" s="8">
-        <v>46331</v>
-      </c>
+      <c r="A92" s="8"/>
       <c r="B92" s="13"/>
       <c r="C92" s="13"/>
       <c r="D92" s="13"/>
@@ -4033,9 +4225,7 @@
       <c r="N92" s="16"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A93" s="8">
-        <v>46332</v>
-      </c>
+      <c r="A93" s="8"/>
       <c r="B93" s="13"/>
       <c r="C93" s="13"/>
       <c r="D93" s="13"/>
@@ -4057,9 +4247,7 @@
       <c r="N93" s="16"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A94" s="8">
-        <v>46333</v>
-      </c>
+      <c r="A94" s="8"/>
       <c r="B94" s="13"/>
       <c r="C94" s="13"/>
       <c r="D94" s="13"/>
@@ -4081,9 +4269,7 @@
       <c r="N94" s="16"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A95" s="8">
-        <v>46334</v>
-      </c>
+      <c r="A95" s="8"/>
       <c r="B95" s="13"/>
       <c r="C95" s="13"/>
       <c r="D95" s="13"/>
@@ -4105,9 +4291,7 @@
       <c r="N95" s="16"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A96" s="8">
-        <v>46335</v>
-      </c>
+      <c r="A96" s="8"/>
       <c r="B96" s="13"/>
       <c r="C96" s="13"/>
       <c r="D96" s="13"/>
@@ -4129,9 +4313,7 @@
       <c r="N96" s="16"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A97" s="8">
-        <v>46336</v>
-      </c>
+      <c r="A97" s="8"/>
       <c r="B97" s="13"/>
       <c r="C97" s="13"/>
       <c r="D97" s="13"/>
@@ -4153,9 +4335,7 @@
       <c r="N97" s="16"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A98" s="8">
-        <v>46337</v>
-      </c>
+      <c r="A98" s="8"/>
       <c r="B98" s="13"/>
       <c r="C98" s="13"/>
       <c r="D98" s="13"/>
@@ -4177,9 +4357,7 @@
       <c r="N98" s="16"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A99" s="8">
-        <v>46338</v>
-      </c>
+      <c r="A99" s="8"/>
       <c r="B99" s="13"/>
       <c r="C99" s="13"/>
       <c r="D99" s="13"/>
@@ -4201,9 +4379,7 @@
       <c r="N99" s="16"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A100" s="8">
-        <v>46339</v>
-      </c>
+      <c r="A100" s="8"/>
       <c r="B100" s="13"/>
       <c r="C100" s="13"/>
       <c r="D100" s="13"/>
@@ -4225,9 +4401,7 @@
       <c r="N100" s="16"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A101" s="8">
-        <v>46340</v>
-      </c>
+      <c r="A101" s="8"/>
       <c r="B101" s="13"/>
       <c r="C101" s="13"/>
       <c r="D101" s="13"/>
@@ -4249,9 +4423,7 @@
       <c r="N101" s="16"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A102" s="8">
-        <v>46341</v>
-      </c>
+      <c r="A102" s="8"/>
       <c r="B102" s="13"/>
       <c r="C102" s="13"/>
       <c r="D102" s="13"/>
@@ -4273,9 +4445,7 @@
       <c r="N102" s="16"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A103" s="8">
-        <v>46342</v>
-      </c>
+      <c r="A103" s="8"/>
       <c r="B103" s="13"/>
       <c r="C103" s="13"/>
       <c r="D103" s="13"/>
@@ -4297,9 +4467,7 @@
       <c r="N103" s="16"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A104" s="8">
-        <v>46343</v>
-      </c>
+      <c r="A104" s="8"/>
       <c r="B104" s="13"/>
       <c r="C104" s="13"/>
       <c r="D104" s="13"/>
@@ -4321,9 +4489,7 @@
       <c r="N104" s="16"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A105" s="8">
-        <v>46344</v>
-      </c>
+      <c r="A105" s="8"/>
       <c r="B105" s="13"/>
       <c r="C105" s="13"/>
       <c r="D105" s="13"/>
@@ -4345,9 +4511,7 @@
       <c r="N105" s="16"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A106" s="8">
-        <v>46345</v>
-      </c>
+      <c r="A106" s="8"/>
       <c r="B106" s="13"/>
       <c r="C106" s="13"/>
       <c r="D106" s="13"/>
@@ -4369,9 +4533,7 @@
       <c r="N106" s="16"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A107" s="8">
-        <v>46346</v>
-      </c>
+      <c r="A107" s="8"/>
       <c r="B107" s="13"/>
       <c r="C107" s="13"/>
       <c r="D107" s="13"/>
@@ -4393,9 +4555,7 @@
       <c r="N107" s="16"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A108" s="8">
-        <v>46347</v>
-      </c>
+      <c r="A108" s="8"/>
       <c r="B108" s="13"/>
       <c r="C108" s="13"/>
       <c r="D108" s="13"/>
@@ -4417,9 +4577,7 @@
       <c r="N108" s="16"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A109" s="8">
-        <v>46348</v>
-      </c>
+      <c r="A109" s="8"/>
       <c r="B109" s="13"/>
       <c r="C109" s="13"/>
       <c r="D109" s="13"/>
@@ -4441,9 +4599,7 @@
       <c r="N109" s="16"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A110" s="8">
-        <v>46349</v>
-      </c>
+      <c r="A110" s="8"/>
       <c r="B110" s="13"/>
       <c r="C110" s="13"/>
       <c r="D110" s="13"/>
@@ -4465,9 +4621,7 @@
       <c r="N110" s="16"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A111" s="8">
-        <v>46350</v>
-      </c>
+      <c r="A111" s="8"/>
       <c r="B111" s="13"/>
       <c r="C111" s="13"/>
       <c r="D111" s="13"/>
@@ -4489,9 +4643,7 @@
       <c r="N111" s="16"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A112" s="8">
-        <v>46351</v>
-      </c>
+      <c r="A112" s="8"/>
       <c r="B112" s="13"/>
       <c r="C112" s="13"/>
       <c r="D112" s="13"/>
@@ -4513,9 +4665,7 @@
       <c r="N112" s="16"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A113" s="8">
-        <v>46352</v>
-      </c>
+      <c r="A113" s="8"/>
       <c r="B113" s="13"/>
       <c r="C113" s="13"/>
       <c r="D113" s="13"/>
@@ -4537,9 +4687,7 @@
       <c r="N113" s="16"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A114" s="8">
-        <v>46353</v>
-      </c>
+      <c r="A114" s="8"/>
       <c r="B114" s="13"/>
       <c r="C114" s="13"/>
       <c r="D114" s="13"/>
@@ -4561,9 +4709,7 @@
       <c r="N114" s="16"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A115" s="8">
-        <v>46354</v>
-      </c>
+      <c r="A115" s="8"/>
       <c r="B115" s="13"/>
       <c r="C115" s="13"/>
       <c r="D115" s="13"/>
@@ -4585,9 +4731,7 @@
       <c r="N115" s="16"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A116" s="8">
-        <v>46355</v>
-      </c>
+      <c r="A116" s="8"/>
       <c r="B116" s="13"/>
       <c r="C116" s="13"/>
       <c r="D116" s="13"/>
@@ -4609,9 +4753,7 @@
       <c r="N116" s="16"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A117" s="8">
-        <v>46356</v>
-      </c>
+      <c r="A117" s="8"/>
       <c r="B117" s="13"/>
       <c r="C117" s="13"/>
       <c r="D117" s="13"/>
@@ -4633,9 +4775,7 @@
       <c r="N117" s="16"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A118" s="8">
-        <v>46357</v>
-      </c>
+      <c r="A118" s="8"/>
       <c r="B118" s="13"/>
       <c r="C118" s="13"/>
       <c r="D118" s="13"/>
@@ -4657,9 +4797,7 @@
       <c r="N118" s="16"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A119" s="8">
-        <v>46358</v>
-      </c>
+      <c r="A119" s="8"/>
       <c r="B119" s="13"/>
       <c r="C119" s="13"/>
       <c r="D119" s="13"/>
@@ -4681,9 +4819,7 @@
       <c r="N119" s="16"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A120" s="8">
-        <v>46359</v>
-      </c>
+      <c r="A120" s="8"/>
       <c r="B120" s="13"/>
       <c r="C120" s="13"/>
       <c r="D120" s="13"/>
@@ -4705,9 +4841,7 @@
       <c r="N120" s="16"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A121" s="8">
-        <v>46360</v>
-      </c>
+      <c r="A121" s="8"/>
       <c r="B121" s="13"/>
       <c r="C121" s="13"/>
       <c r="D121" s="13"/>
@@ -4729,9 +4863,7 @@
       <c r="N121" s="16"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A122" s="8">
-        <v>46361</v>
-      </c>
+      <c r="A122" s="8"/>
       <c r="B122" s="13"/>
       <c r="C122" s="13"/>
       <c r="D122" s="13"/>
@@ -4753,9 +4885,7 @@
       <c r="N122" s="16"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A123" s="8">
-        <v>46362</v>
-      </c>
+      <c r="A123" s="8"/>
       <c r="B123" s="13"/>
       <c r="C123" s="13"/>
       <c r="D123" s="13"/>
@@ -4777,9 +4907,7 @@
       <c r="N123" s="16"/>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A124" s="8">
-        <v>46363</v>
-      </c>
+      <c r="A124" s="8"/>
       <c r="B124" s="13"/>
       <c r="C124" s="13"/>
       <c r="D124" s="13"/>
@@ -4801,9 +4929,7 @@
       <c r="N124" s="16"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A125" s="8">
-        <v>46364</v>
-      </c>
+      <c r="A125" s="8"/>
       <c r="B125" s="13"/>
       <c r="C125" s="13"/>
       <c r="D125" s="13"/>
@@ -4825,9 +4951,7 @@
       <c r="N125" s="16"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A126" s="8">
-        <v>46365</v>
-      </c>
+      <c r="A126" s="8"/>
       <c r="B126" s="13"/>
       <c r="C126" s="13"/>
       <c r="D126" s="13"/>
@@ -4849,9 +4973,7 @@
       <c r="N126" s="16"/>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A127" s="8">
-        <v>46366</v>
-      </c>
+      <c r="A127" s="8"/>
       <c r="B127" s="13"/>
       <c r="C127" s="13"/>
       <c r="D127" s="13"/>
@@ -4873,9 +4995,7 @@
       <c r="N127" s="16"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A128" s="8">
-        <v>46367</v>
-      </c>
+      <c r="A128" s="8"/>
       <c r="B128" s="13"/>
       <c r="C128" s="13"/>
       <c r="D128" s="13"/>
@@ -4897,9 +5017,7 @@
       <c r="N128" s="16"/>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A129" s="8">
-        <v>46368</v>
-      </c>
+      <c r="A129" s="8"/>
       <c r="B129" s="13"/>
       <c r="C129" s="13"/>
       <c r="D129" s="13"/>
@@ -4921,9 +5039,7 @@
       <c r="N129" s="16"/>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A130" s="8">
-        <v>46369</v>
-      </c>
+      <c r="A130" s="8"/>
       <c r="B130" s="13"/>
       <c r="C130" s="13"/>
       <c r="D130" s="13"/>
@@ -4945,9 +5061,7 @@
       <c r="N130" s="16"/>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A131" s="8">
-        <v>46370</v>
-      </c>
+      <c r="A131" s="8"/>
       <c r="B131" s="13"/>
       <c r="C131" s="13"/>
       <c r="D131" s="13"/>
@@ -4969,9 +5083,7 @@
       <c r="N131" s="16"/>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A132" s="8">
-        <v>46371</v>
-      </c>
+      <c r="A132" s="8"/>
       <c r="B132" s="13"/>
       <c r="C132" s="13"/>
       <c r="D132" s="13"/>
@@ -4993,9 +5105,7 @@
       <c r="N132" s="16"/>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A133" s="8">
-        <v>46372</v>
-      </c>
+      <c r="A133" s="8"/>
       <c r="B133" s="13"/>
       <c r="C133" s="13"/>
       <c r="D133" s="13"/>
@@ -5017,9 +5127,7 @@
       <c r="N133" s="16"/>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A134" s="8">
-        <v>46373</v>
-      </c>
+      <c r="A134" s="8"/>
       <c r="B134" s="13"/>
       <c r="C134" s="13"/>
       <c r="D134" s="13"/>
@@ -5041,9 +5149,7 @@
       <c r="N134" s="16"/>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A135" s="8">
-        <v>46374</v>
-      </c>
+      <c r="A135" s="8"/>
       <c r="B135" s="13"/>
       <c r="C135" s="13"/>
       <c r="D135" s="13"/>
@@ -5065,9 +5171,7 @@
       <c r="N135" s="16"/>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A136" s="8">
-        <v>46375</v>
-      </c>
+      <c r="A136" s="8"/>
       <c r="B136" s="13"/>
       <c r="C136" s="13"/>
       <c r="D136" s="13"/>
@@ -5089,9 +5193,7 @@
       <c r="N136" s="16"/>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A137" s="8">
-        <v>46376</v>
-      </c>
+      <c r="A137" s="8"/>
       <c r="B137" s="13"/>
       <c r="C137" s="13"/>
       <c r="D137" s="13"/>
@@ -5113,9 +5215,7 @@
       <c r="N137" s="16"/>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A138" s="8">
-        <v>46377</v>
-      </c>
+      <c r="A138" s="8"/>
       <c r="B138" s="13"/>
       <c r="C138" s="13"/>
       <c r="D138" s="13"/>
@@ -5137,9 +5237,7 @@
       <c r="N138" s="16"/>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A139" s="8">
-        <v>46378</v>
-      </c>
+      <c r="A139" s="8"/>
       <c r="B139" s="13"/>
       <c r="C139" s="13"/>
       <c r="D139" s="13"/>
@@ -5161,9 +5259,7 @@
       <c r="N139" s="16"/>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A140" s="8">
-        <v>46379</v>
-      </c>
+      <c r="A140" s="8"/>
       <c r="B140" s="13"/>
       <c r="C140" s="13"/>
       <c r="D140" s="13"/>
@@ -5185,9 +5281,7 @@
       <c r="N140" s="16"/>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A141" s="8">
-        <v>46380</v>
-      </c>
+      <c r="A141" s="8"/>
       <c r="B141" s="13"/>
       <c r="C141" s="13"/>
       <c r="D141" s="13"/>
@@ -5209,9 +5303,7 @@
       <c r="N141" s="16"/>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A142" s="8">
-        <v>46381</v>
-      </c>
+      <c r="A142" s="8"/>
       <c r="B142" s="13"/>
       <c r="C142" s="13"/>
       <c r="D142" s="13"/>
@@ -5233,9 +5325,7 @@
       <c r="N142" s="16"/>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A143" s="8">
-        <v>46382</v>
-      </c>
+      <c r="A143" s="8"/>
       <c r="B143" s="13"/>
       <c r="C143" s="13"/>
       <c r="D143" s="13"/>
@@ -5257,9 +5347,7 @@
       <c r="N143" s="16"/>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A144" s="8">
-        <v>46383</v>
-      </c>
+      <c r="A144" s="8"/>
       <c r="B144" s="13"/>
       <c r="C144" s="13"/>
       <c r="D144" s="13"/>
@@ -5281,9 +5369,7 @@
       <c r="N144" s="16"/>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A145" s="8">
-        <v>46384</v>
-      </c>
+      <c r="A145" s="8"/>
       <c r="B145" s="13"/>
       <c r="C145" s="13"/>
       <c r="D145" s="13"/>
@@ -5305,9 +5391,7 @@
       <c r="N145" s="16"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A146" s="8">
-        <v>46385</v>
-      </c>
+      <c r="A146" s="8"/>
       <c r="B146" s="13"/>
       <c r="C146" s="13"/>
       <c r="D146" s="13"/>
@@ -5329,9 +5413,7 @@
       <c r="N146" s="16"/>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A147" s="8">
-        <v>46386</v>
-      </c>
+      <c r="A147" s="8"/>
       <c r="B147" s="13"/>
       <c r="C147" s="13"/>
       <c r="D147" s="13"/>
@@ -5353,9 +5435,7 @@
       <c r="N147" s="16"/>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A148" s="8">
-        <v>46387</v>
-      </c>
+      <c r="A148" s="8"/>
       <c r="B148" s="13"/>
       <c r="C148" s="13"/>
       <c r="D148" s="13"/>
@@ -5377,9 +5457,7 @@
       <c r="N148" s="16"/>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A149" s="8">
-        <v>46388</v>
-      </c>
+      <c r="A149" s="8"/>
       <c r="B149" s="13"/>
       <c r="C149" s="13"/>
       <c r="D149" s="13"/>
@@ -5401,9 +5479,7 @@
       <c r="N149" s="16"/>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A150" s="8">
-        <v>46389</v>
-      </c>
+      <c r="A150" s="8"/>
       <c r="B150" s="13"/>
       <c r="C150" s="13"/>
       <c r="D150" s="13"/>
@@ -5425,9 +5501,7 @@
       <c r="N150" s="16"/>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A151" s="8">
-        <v>46390</v>
-      </c>
+      <c r="A151" s="8"/>
       <c r="B151" s="13"/>
       <c r="C151" s="13"/>
       <c r="D151" s="13"/>
@@ -5449,9 +5523,7 @@
       <c r="N151" s="16"/>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A152" s="8">
-        <v>46391</v>
-      </c>
+      <c r="A152" s="8"/>
       <c r="B152" s="13"/>
       <c r="C152" s="13"/>
       <c r="D152" s="13"/>
@@ -5473,9 +5545,7 @@
       <c r="N152" s="16"/>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A153" s="8">
-        <v>46392</v>
-      </c>
+      <c r="A153" s="8"/>
       <c r="B153" s="13"/>
       <c r="C153" s="13"/>
       <c r="D153" s="13"/>
@@ -5497,9 +5567,7 @@
       <c r="N153" s="16"/>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A154" s="8">
-        <v>46393</v>
-      </c>
+      <c r="A154" s="8"/>
       <c r="B154" s="13"/>
       <c r="C154" s="13"/>
       <c r="D154" s="13"/>
@@ -5521,9 +5589,7 @@
       <c r="N154" s="16"/>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A155" s="8">
-        <v>46394</v>
-      </c>
+      <c r="A155" s="8"/>
       <c r="B155" s="13"/>
       <c r="C155" s="13"/>
       <c r="D155" s="13"/>
@@ -5545,9 +5611,7 @@
       <c r="N155" s="16"/>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A156" s="8">
-        <v>46395</v>
-      </c>
+      <c r="A156" s="8"/>
       <c r="B156" s="13"/>
       <c r="C156" s="13"/>
       <c r="D156" s="13"/>
@@ -5569,9 +5633,7 @@
       <c r="N156" s="16"/>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A157" s="8">
-        <v>46396</v>
-      </c>
+      <c r="A157" s="8"/>
       <c r="B157" s="13"/>
       <c r="C157" s="13"/>
       <c r="D157" s="13"/>
@@ -5593,9 +5655,7 @@
       <c r="N157" s="16"/>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A158" s="8">
-        <v>46397</v>
-      </c>
+      <c r="A158" s="8"/>
       <c r="B158" s="13"/>
       <c r="C158" s="13"/>
       <c r="D158" s="13"/>
@@ -5617,9 +5677,7 @@
       <c r="N158" s="16"/>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A159" s="8">
-        <v>46398</v>
-      </c>
+      <c r="A159" s="8"/>
       <c r="B159" s="13"/>
       <c r="C159" s="13"/>
       <c r="D159" s="13"/>
@@ -5641,9 +5699,7 @@
       <c r="N159" s="16"/>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A160" s="8">
-        <v>46399</v>
-      </c>
+      <c r="A160" s="8"/>
       <c r="B160" s="13"/>
       <c r="C160" s="13"/>
       <c r="D160" s="13"/>
@@ -5665,9 +5721,7 @@
       <c r="N160" s="16"/>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A161" s="8">
-        <v>46400</v>
-      </c>
+      <c r="A161" s="8"/>
       <c r="B161" s="13"/>
       <c r="C161" s="13"/>
       <c r="D161" s="13"/>
@@ -5689,9 +5743,7 @@
       <c r="N161" s="16"/>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A162" s="8">
-        <v>46401</v>
-      </c>
+      <c r="A162" s="8"/>
       <c r="B162" s="13"/>
       <c r="C162" s="13"/>
       <c r="D162" s="13"/>
@@ -5713,9 +5765,7 @@
       <c r="N162" s="16"/>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A163" s="8">
-        <v>46402</v>
-      </c>
+      <c r="A163" s="8"/>
       <c r="B163" s="13"/>
       <c r="C163" s="13"/>
       <c r="D163" s="13"/>
@@ -5737,9 +5787,7 @@
       <c r="N163" s="16"/>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A164" s="8">
-        <v>46403</v>
-      </c>
+      <c r="A164" s="8"/>
       <c r="B164" s="13"/>
       <c r="C164" s="13"/>
       <c r="D164" s="13"/>
@@ -5761,9 +5809,7 @@
       <c r="N164" s="16"/>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A165" s="8">
-        <v>46404</v>
-      </c>
+      <c r="A165" s="8"/>
       <c r="B165" s="13"/>
       <c r="C165" s="13"/>
       <c r="D165" s="13"/>
@@ -5785,9 +5831,7 @@
       <c r="N165" s="16"/>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A166" s="8">
-        <v>46405</v>
-      </c>
+      <c r="A166" s="8"/>
       <c r="B166" s="13"/>
       <c r="C166" s="13"/>
       <c r="D166" s="13"/>
@@ -5809,9 +5853,7 @@
       <c r="N166" s="16"/>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A167" s="8">
-        <v>46406</v>
-      </c>
+      <c r="A167" s="8"/>
       <c r="B167" s="13"/>
       <c r="C167" s="13"/>
       <c r="D167" s="13"/>
@@ -5833,9 +5875,7 @@
       <c r="N167" s="16"/>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A168" s="8">
-        <v>46407</v>
-      </c>
+      <c r="A168" s="8"/>
       <c r="B168" s="13"/>
       <c r="C168" s="13"/>
       <c r="D168" s="13"/>
@@ -5857,9 +5897,7 @@
       <c r="N168" s="16"/>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A169" s="8">
-        <v>46408</v>
-      </c>
+      <c r="A169" s="8"/>
       <c r="B169" s="13"/>
       <c r="C169" s="13"/>
       <c r="D169" s="13"/>
@@ -5881,9 +5919,7 @@
       <c r="N169" s="16"/>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A170" s="8">
-        <v>46409</v>
-      </c>
+      <c r="A170" s="8"/>
       <c r="B170" s="13"/>
       <c r="C170" s="13"/>
       <c r="D170" s="13"/>
@@ -5905,9 +5941,7 @@
       <c r="N170" s="16"/>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A171" s="8">
-        <v>46410</v>
-      </c>
+      <c r="A171" s="8"/>
       <c r="B171" s="13"/>
       <c r="C171" s="13"/>
       <c r="D171" s="13"/>
@@ -5929,9 +5963,7 @@
       <c r="N171" s="16"/>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A172" s="8">
-        <v>46411</v>
-      </c>
+      <c r="A172" s="8"/>
       <c r="B172" s="13"/>
       <c r="C172" s="13"/>
       <c r="D172" s="13"/>
@@ -5953,9 +5985,7 @@
       <c r="N172" s="16"/>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A173" s="8">
-        <v>46412</v>
-      </c>
+      <c r="A173" s="8"/>
       <c r="B173" s="13"/>
       <c r="C173" s="13"/>
       <c r="D173" s="13"/>
@@ -5977,9 +6007,7 @@
       <c r="N173" s="16"/>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A174" s="8">
-        <v>46413</v>
-      </c>
+      <c r="A174" s="8"/>
       <c r="B174" s="13"/>
       <c r="C174" s="13"/>
       <c r="D174" s="13"/>
@@ -6001,9 +6029,7 @@
       <c r="N174" s="16"/>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A175" s="8">
-        <v>46414</v>
-      </c>
+      <c r="A175" s="8"/>
       <c r="B175" s="13"/>
       <c r="C175" s="13"/>
       <c r="D175" s="13"/>
@@ -6025,9 +6051,7 @@
       <c r="N175" s="16"/>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A176" s="8">
-        <v>46415</v>
-      </c>
+      <c r="A176" s="8"/>
       <c r="B176" s="13"/>
       <c r="C176" s="13"/>
       <c r="D176" s="13"/>
@@ -6049,9 +6073,7 @@
       <c r="N176" s="16"/>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A177" s="8">
-        <v>46416</v>
-      </c>
+      <c r="A177" s="8"/>
       <c r="B177" s="13"/>
       <c r="C177" s="13"/>
       <c r="D177" s="13"/>
@@ -6073,9 +6095,7 @@
       <c r="N177" s="16"/>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A178" s="8">
-        <v>46417</v>
-      </c>
+      <c r="A178" s="8"/>
       <c r="B178" s="13"/>
       <c r="C178" s="13"/>
       <c r="D178" s="13"/>
@@ -6097,9 +6117,7 @@
       <c r="N178" s="16"/>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A179" s="8">
-        <v>46418</v>
-      </c>
+      <c r="A179" s="8"/>
       <c r="B179" s="13"/>
       <c r="C179" s="13"/>
       <c r="D179" s="13"/>
@@ -6121,9 +6139,7 @@
       <c r="N179" s="16"/>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A180" s="8">
-        <v>46419</v>
-      </c>
+      <c r="A180" s="8"/>
       <c r="B180" s="13"/>
       <c r="C180" s="13"/>
       <c r="D180" s="13"/>
@@ -6145,9 +6161,7 @@
       <c r="N180" s="16"/>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A181" s="8">
-        <v>46420</v>
-      </c>
+      <c r="A181" s="8"/>
       <c r="B181" s="13"/>
       <c r="C181" s="13"/>
       <c r="D181" s="13"/>
@@ -6169,9 +6183,7 @@
       <c r="N181" s="16"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A182" s="8">
-        <v>46421</v>
-      </c>
+      <c r="A182" s="8"/>
       <c r="B182" s="13"/>
       <c r="C182" s="13"/>
       <c r="D182" s="13"/>
@@ -6193,9 +6205,7 @@
       <c r="N182" s="16"/>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A183" s="8">
-        <v>46422</v>
-      </c>
+      <c r="A183" s="8"/>
       <c r="B183" s="13"/>
       <c r="C183" s="13"/>
       <c r="D183" s="13"/>
@@ -6217,9 +6227,7 @@
       <c r="N183" s="16"/>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A184" s="8">
-        <v>46423</v>
-      </c>
+      <c r="A184" s="8"/>
       <c r="B184" s="13"/>
       <c r="C184" s="13"/>
       <c r="D184" s="13"/>
@@ -6241,9 +6249,7 @@
       <c r="N184" s="16"/>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A185" s="8">
-        <v>46424</v>
-      </c>
+      <c r="A185" s="8"/>
       <c r="B185" s="13"/>
       <c r="C185" s="13"/>
       <c r="D185" s="13"/>
@@ -6265,9 +6271,7 @@
       <c r="N185" s="16"/>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A186" s="8">
-        <v>46425</v>
-      </c>
+      <c r="A186" s="8"/>
       <c r="B186" s="13"/>
       <c r="C186" s="13"/>
       <c r="D186" s="13"/>
@@ -6289,9 +6293,7 @@
       <c r="N186" s="16"/>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A187" s="8">
-        <v>46426</v>
-      </c>
+      <c r="A187" s="8"/>
       <c r="B187" s="13"/>
       <c r="C187" s="13"/>
       <c r="D187" s="13"/>
@@ -6313,9 +6315,7 @@
       <c r="N187" s="16"/>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A188" s="8">
-        <v>46427</v>
-      </c>
+      <c r="A188" s="8"/>
       <c r="B188" s="13"/>
       <c r="C188" s="13"/>
       <c r="D188" s="13"/>
@@ -6337,9 +6337,7 @@
       <c r="N188" s="16"/>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A189" s="8">
-        <v>46428</v>
-      </c>
+      <c r="A189" s="8"/>
       <c r="B189" s="13"/>
       <c r="C189" s="13"/>
       <c r="D189" s="13"/>
@@ -6361,9 +6359,7 @@
       <c r="N189" s="16"/>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A190" s="8">
-        <v>46429</v>
-      </c>
+      <c r="A190" s="8"/>
       <c r="B190" s="13"/>
       <c r="C190" s="13"/>
       <c r="D190" s="13"/>
@@ -6385,9 +6381,7 @@
       <c r="N190" s="16"/>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A191" s="8">
-        <v>46430</v>
-      </c>
+      <c r="A191" s="8"/>
       <c r="B191" s="13"/>
       <c r="C191" s="13"/>
       <c r="D191" s="13"/>
@@ -6409,9 +6403,7 @@
       <c r="N191" s="16"/>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A192" s="8">
-        <v>46431</v>
-      </c>
+      <c r="A192" s="8"/>
       <c r="B192" s="13"/>
       <c r="C192" s="13"/>
       <c r="D192" s="13"/>
@@ -6433,9 +6425,7 @@
       <c r="N192" s="16"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A193" s="8">
-        <v>46432</v>
-      </c>
+      <c r="A193" s="8"/>
       <c r="B193" s="13"/>
       <c r="C193" s="13"/>
       <c r="D193" s="13"/>
@@ -6457,9 +6447,7 @@
       <c r="N193" s="16"/>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A194" s="8">
-        <v>46433</v>
-      </c>
+      <c r="A194" s="8"/>
       <c r="B194" s="13"/>
       <c r="C194" s="13"/>
       <c r="D194" s="13"/>
@@ -6481,9 +6469,7 @@
       <c r="N194" s="16"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A195" s="8">
-        <v>46434</v>
-      </c>
+      <c r="A195" s="8"/>
       <c r="B195" s="13"/>
       <c r="C195" s="13"/>
       <c r="D195" s="13"/>
@@ -6505,9 +6491,7 @@
       <c r="N195" s="16"/>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A196" s="8">
-        <v>46435</v>
-      </c>
+      <c r="A196" s="8"/>
       <c r="B196" s="13"/>
       <c r="C196" s="13"/>
       <c r="D196" s="13"/>
@@ -6529,9 +6513,7 @@
       <c r="N196" s="16"/>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A197" s="8">
-        <v>46436</v>
-      </c>
+      <c r="A197" s="8"/>
       <c r="B197" s="13"/>
       <c r="C197" s="13"/>
       <c r="D197" s="13"/>
@@ -6553,9 +6535,7 @@
       <c r="N197" s="16"/>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A198" s="8">
-        <v>46437</v>
-      </c>
+      <c r="A198" s="8"/>
       <c r="B198" s="13"/>
       <c r="C198" s="13"/>
       <c r="D198" s="13"/>
@@ -6577,9 +6557,7 @@
       <c r="N198" s="16"/>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A199" s="8">
-        <v>46438</v>
-      </c>
+      <c r="A199" s="8"/>
       <c r="B199" s="13"/>
       <c r="C199" s="13"/>
       <c r="D199" s="13"/>
@@ -6601,9 +6579,7 @@
       <c r="N199" s="16"/>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A200" s="8">
-        <v>46439</v>
-      </c>
+      <c r="A200" s="8"/>
       <c r="B200" s="13"/>
       <c r="C200" s="13"/>
       <c r="D200" s="13"/>
@@ -6625,9 +6601,7 @@
       <c r="N200" s="16"/>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A201" s="8">
-        <v>46440</v>
-      </c>
+      <c r="A201" s="8"/>
       <c r="B201" s="13"/>
       <c r="C201" s="13"/>
       <c r="D201" s="13"/>
@@ -6649,9 +6623,7 @@
       <c r="N201" s="16"/>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A202" s="8">
-        <v>46441</v>
-      </c>
+      <c r="A202" s="8"/>
       <c r="B202" s="13"/>
       <c r="C202" s="13"/>
       <c r="D202" s="13"/>
@@ -6673,9 +6645,7 @@
       <c r="N202" s="16"/>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A203" s="8">
-        <v>46442</v>
-      </c>
+      <c r="A203" s="8"/>
       <c r="B203" s="13"/>
       <c r="C203" s="13"/>
       <c r="D203" s="13"/>
@@ -6697,9 +6667,7 @@
       <c r="N203" s="16"/>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A204" s="8">
-        <v>46443</v>
-      </c>
+      <c r="A204" s="8"/>
       <c r="B204" s="13"/>
       <c r="C204" s="13"/>
       <c r="D204" s="13"/>
@@ -6721,9 +6689,7 @@
       <c r="N204" s="16"/>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A205" s="8">
-        <v>46444</v>
-      </c>
+      <c r="A205" s="8"/>
       <c r="B205" s="13"/>
       <c r="C205" s="13"/>
       <c r="D205" s="13"/>
@@ -6745,9 +6711,7 @@
       <c r="N205" s="16"/>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A206" s="8">
-        <v>46445</v>
-      </c>
+      <c r="A206" s="8"/>
       <c r="B206" s="13"/>
       <c r="C206" s="13"/>
       <c r="D206" s="13"/>
@@ -6769,9 +6733,7 @@
       <c r="N206" s="16"/>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A207" s="8">
-        <v>46446</v>
-      </c>
+      <c r="A207" s="8"/>
       <c r="B207" s="13"/>
       <c r="C207" s="13"/>
       <c r="D207" s="13"/>
@@ -6793,9 +6755,7 @@
       <c r="N207" s="16"/>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A208" s="8">
-        <v>46447</v>
-      </c>
+      <c r="A208" s="8"/>
       <c r="B208" s="13"/>
       <c r="C208" s="13"/>
       <c r="D208" s="13"/>
@@ -6817,9 +6777,7 @@
       <c r="N208" s="16"/>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A209" s="8">
-        <v>46448</v>
-      </c>
+      <c r="A209" s="8"/>
       <c r="B209" s="13"/>
       <c r="C209" s="13"/>
       <c r="D209" s="13"/>
@@ -6841,9 +6799,7 @@
       <c r="N209" s="16"/>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A210" s="8">
-        <v>46449</v>
-      </c>
+      <c r="A210" s="8"/>
       <c r="B210" s="13"/>
       <c r="C210" s="13"/>
       <c r="D210" s="13"/>
@@ -6865,9 +6821,7 @@
       <c r="N210" s="16"/>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A211" s="8">
-        <v>46450</v>
-      </c>
+      <c r="A211" s="8"/>
       <c r="B211" s="13"/>
       <c r="C211" s="13"/>
       <c r="D211" s="13"/>
@@ -6889,9 +6843,7 @@
       <c r="N211" s="16"/>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A212" s="8">
-        <v>46451</v>
-      </c>
+      <c r="A212" s="8"/>
       <c r="B212" s="13"/>
       <c r="C212" s="13"/>
       <c r="D212" s="13"/>
@@ -6913,9 +6865,7 @@
       <c r="N212" s="16"/>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A213" s="8">
-        <v>46452</v>
-      </c>
+      <c r="A213" s="8"/>
       <c r="B213" s="13"/>
       <c r="C213" s="13"/>
       <c r="D213" s="13"/>
@@ -6937,9 +6887,7 @@
       <c r="N213" s="16"/>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A214" s="8">
-        <v>46453</v>
-      </c>
+      <c r="A214" s="8"/>
       <c r="B214" s="13"/>
       <c r="C214" s="13"/>
       <c r="D214" s="13"/>
@@ -6961,9 +6909,7 @@
       <c r="N214" s="16"/>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A215" s="8">
-        <v>46454</v>
-      </c>
+      <c r="A215" s="8"/>
       <c r="B215" s="13"/>
       <c r="C215" s="13"/>
       <c r="D215" s="13"/>
@@ -6985,9 +6931,7 @@
       <c r="N215" s="16"/>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A216" s="8">
-        <v>46455</v>
-      </c>
+      <c r="A216" s="8"/>
       <c r="B216" s="13"/>
       <c r="C216" s="13"/>
       <c r="D216" s="13"/>
@@ -7009,9 +6953,7 @@
       <c r="N216" s="16"/>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A217" s="8">
-        <v>46456</v>
-      </c>
+      <c r="A217" s="8"/>
       <c r="B217" s="13"/>
       <c r="C217" s="13"/>
       <c r="D217" s="13"/>
@@ -7033,9 +6975,7 @@
       <c r="N217" s="16"/>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A218" s="8">
-        <v>46457</v>
-      </c>
+      <c r="A218" s="8"/>
       <c r="B218" s="13"/>
       <c r="C218" s="13"/>
       <c r="D218" s="13"/>
@@ -7057,9 +6997,7 @@
       <c r="N218" s="16"/>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A219" s="8">
-        <v>46458</v>
-      </c>
+      <c r="A219" s="8"/>
       <c r="B219" s="13"/>
       <c r="C219" s="13"/>
       <c r="D219" s="13"/>
@@ -7081,9 +7019,7 @@
       <c r="N219" s="16"/>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A220" s="8">
-        <v>46459</v>
-      </c>
+      <c r="A220" s="8"/>
       <c r="B220" s="13"/>
       <c r="C220" s="13"/>
       <c r="D220" s="13"/>
@@ -7105,9 +7041,7 @@
       <c r="N220" s="16"/>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A221" s="8">
-        <v>46460</v>
-      </c>
+      <c r="A221" s="8"/>
       <c r="B221" s="13"/>
       <c r="C221" s="13"/>
       <c r="D221" s="13"/>
@@ -7129,9 +7063,7 @@
       <c r="N221" s="16"/>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A222" s="8">
-        <v>46461</v>
-      </c>
+      <c r="A222" s="8"/>
       <c r="B222" s="13"/>
       <c r="C222" s="13"/>
       <c r="D222" s="13"/>
@@ -7153,9 +7085,7 @@
       <c r="N222" s="16"/>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A223" s="8">
-        <v>46462</v>
-      </c>
+      <c r="A223" s="8"/>
       <c r="B223" s="13"/>
       <c r="C223" s="13"/>
       <c r="D223" s="13"/>
@@ -7177,9 +7107,7 @@
       <c r="N223" s="16"/>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A224" s="8">
-        <v>46463</v>
-      </c>
+      <c r="A224" s="8"/>
       <c r="B224" s="13"/>
       <c r="C224" s="13"/>
       <c r="D224" s="13"/>
@@ -7201,9 +7129,7 @@
       <c r="N224" s="16"/>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A225" s="8">
-        <v>46464</v>
-      </c>
+      <c r="A225" s="8"/>
       <c r="B225" s="13"/>
       <c r="C225" s="13"/>
       <c r="D225" s="13"/>
@@ -7225,9 +7151,7 @@
       <c r="N225" s="16"/>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A226" s="8">
-        <v>46465</v>
-      </c>
+      <c r="A226" s="8"/>
       <c r="B226" s="13"/>
       <c r="C226" s="13"/>
       <c r="D226" s="13"/>
@@ -7249,9 +7173,7 @@
       <c r="N226" s="16"/>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A227" s="8">
-        <v>46466</v>
-      </c>
+      <c r="A227" s="8"/>
       <c r="B227" s="13"/>
       <c r="C227" s="13"/>
       <c r="D227" s="13"/>
@@ -7273,9 +7195,7 @@
       <c r="N227" s="16"/>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A228" s="8">
-        <v>46467</v>
-      </c>
+      <c r="A228" s="8"/>
       <c r="B228" s="13"/>
       <c r="C228" s="13"/>
       <c r="D228" s="13"/>
@@ -7297,9 +7217,7 @@
       <c r="N228" s="16"/>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A229" s="8">
-        <v>46468</v>
-      </c>
+      <c r="A229" s="8"/>
       <c r="B229" s="13"/>
       <c r="C229" s="13"/>
       <c r="D229" s="13"/>
@@ -7321,9 +7239,7 @@
       <c r="N229" s="16"/>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A230" s="8">
-        <v>46469</v>
-      </c>
+      <c r="A230" s="8"/>
       <c r="B230" s="13"/>
       <c r="C230" s="13"/>
       <c r="D230" s="13"/>
@@ -7345,9 +7261,7 @@
       <c r="N230" s="16"/>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A231" s="8">
-        <v>46470</v>
-      </c>
+      <c r="A231" s="8"/>
       <c r="B231" s="13"/>
       <c r="C231" s="13"/>
       <c r="D231" s="13"/>
@@ -7369,9 +7283,7 @@
       <c r="N231" s="16"/>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A232" s="8">
-        <v>46471</v>
-      </c>
+      <c r="A232" s="8"/>
       <c r="B232" s="13"/>
       <c r="C232" s="13"/>
       <c r="D232" s="13"/>
@@ -7393,9 +7305,7 @@
       <c r="N232" s="16"/>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A233" s="8">
-        <v>46472</v>
-      </c>
+      <c r="A233" s="8"/>
       <c r="B233" s="13"/>
       <c r="C233" s="13"/>
       <c r="D233" s="13"/>
@@ -7417,9 +7327,7 @@
       <c r="N233" s="16"/>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A234" s="8">
-        <v>46473</v>
-      </c>
+      <c r="A234" s="8"/>
       <c r="B234" s="13"/>
       <c r="C234" s="13"/>
       <c r="D234" s="13"/>
@@ -7441,9 +7349,7 @@
       <c r="N234" s="16"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A235" s="8">
-        <v>46474</v>
-      </c>
+      <c r="A235" s="8"/>
       <c r="B235" s="13"/>
       <c r="C235" s="13"/>
       <c r="D235" s="13"/>
@@ -7465,9 +7371,7 @@
       <c r="N235" s="16"/>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A236" s="8">
-        <v>46475</v>
-      </c>
+      <c r="A236" s="8"/>
       <c r="B236" s="13"/>
       <c r="C236" s="13"/>
       <c r="D236" s="13"/>
@@ -7489,9 +7393,7 @@
       <c r="N236" s="16"/>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A237" s="8">
-        <v>46476</v>
-      </c>
+      <c r="A237" s="8"/>
       <c r="B237" s="13"/>
       <c r="C237" s="13"/>
       <c r="D237" s="13"/>
@@ -7513,9 +7415,7 @@
       <c r="N237" s="16"/>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A238" s="8">
-        <v>46477</v>
-      </c>
+      <c r="A238" s="8"/>
       <c r="B238" s="13"/>
       <c r="C238" s="13"/>
       <c r="D238" s="13"/>
@@ -7537,9 +7437,7 @@
       <c r="N238" s="16"/>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A239" s="8">
-        <v>46478</v>
-      </c>
+      <c r="A239" s="8"/>
       <c r="B239" s="13"/>
       <c r="C239" s="13"/>
       <c r="D239" s="13"/>
@@ -7561,9 +7459,7 @@
       <c r="N239" s="16"/>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A240" s="8">
-        <v>46479</v>
-      </c>
+      <c r="A240" s="8"/>
       <c r="B240" s="13"/>
       <c r="C240" s="13"/>
       <c r="D240" s="13"/>
@@ -7585,9 +7481,7 @@
       <c r="N240" s="16"/>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A241" s="8">
-        <v>46480</v>
-      </c>
+      <c r="A241" s="8"/>
       <c r="B241" s="13"/>
       <c r="C241" s="13"/>
       <c r="D241" s="13"/>
@@ -7609,9 +7503,7 @@
       <c r="N241" s="16"/>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A242" s="8">
-        <v>46481</v>
-      </c>
+      <c r="A242" s="8"/>
       <c r="B242" s="13"/>
       <c r="C242" s="13"/>
       <c r="D242" s="13"/>
@@ -7633,9 +7525,7 @@
       <c r="N242" s="16"/>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A243" s="8">
-        <v>46482</v>
-      </c>
+      <c r="A243" s="8"/>
       <c r="B243" s="13"/>
       <c r="C243" s="13"/>
       <c r="D243" s="13"/>
@@ -7657,9 +7547,7 @@
       <c r="N243" s="16"/>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A244" s="8">
-        <v>46483</v>
-      </c>
+      <c r="A244" s="8"/>
       <c r="B244" s="13"/>
       <c r="C244" s="13"/>
       <c r="D244" s="13"/>
@@ -7681,9 +7569,7 @@
       <c r="N244" s="16"/>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A245" s="8">
-        <v>46484</v>
-      </c>
+      <c r="A245" s="8"/>
       <c r="B245" s="13"/>
       <c r="C245" s="13"/>
       <c r="D245" s="13"/>
@@ -7705,9 +7591,7 @@
       <c r="N245" s="16"/>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A246" s="8">
-        <v>46485</v>
-      </c>
+      <c r="A246" s="8"/>
       <c r="B246" s="13"/>
       <c r="C246" s="13"/>
       <c r="D246" s="13"/>
@@ -7729,9 +7613,7 @@
       <c r="N246" s="16"/>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A247" s="8">
-        <v>46486</v>
-      </c>
+      <c r="A247" s="8"/>
       <c r="B247" s="13"/>
       <c r="C247" s="13"/>
       <c r="D247" s="13"/>
@@ -7753,9 +7635,7 @@
       <c r="N247" s="16"/>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A248" s="8">
-        <v>46487</v>
-      </c>
+      <c r="A248" s="8"/>
       <c r="B248" s="13"/>
       <c r="C248" s="13"/>
       <c r="D248" s="13"/>
@@ -7777,9 +7657,7 @@
       <c r="N248" s="16"/>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A249" s="8">
-        <v>46488</v>
-      </c>
+      <c r="A249" s="8"/>
       <c r="B249" s="13"/>
       <c r="C249" s="13"/>
       <c r="D249" s="13"/>
@@ -7801,9 +7679,7 @@
       <c r="N249" s="16"/>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A250" s="8">
-        <v>46489</v>
-      </c>
+      <c r="A250" s="8"/>
       <c r="B250" s="13"/>
       <c r="C250" s="13"/>
       <c r="D250" s="13"/>
@@ -7825,9 +7701,7 @@
       <c r="N250" s="16"/>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A251" s="8">
-        <v>46490</v>
-      </c>
+      <c r="A251" s="8"/>
       <c r="B251" s="13"/>
       <c r="C251" s="13"/>
       <c r="D251" s="13"/>
@@ -7849,9 +7723,7 @@
       <c r="N251" s="16"/>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A252" s="8">
-        <v>46491</v>
-      </c>
+      <c r="A252" s="8"/>
       <c r="B252" s="13"/>
       <c r="C252" s="13"/>
       <c r="D252" s="13"/>
@@ -7873,9 +7745,7 @@
       <c r="N252" s="16"/>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A253" s="8">
-        <v>46492</v>
-      </c>
+      <c r="A253" s="8"/>
       <c r="B253" s="13"/>
       <c r="C253" s="13"/>
       <c r="D253" s="13"/>
@@ -7897,9 +7767,7 @@
       <c r="N253" s="16"/>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A254" s="8">
-        <v>46493</v>
-      </c>
+      <c r="A254" s="8"/>
       <c r="B254" s="13"/>
       <c r="C254" s="13"/>
       <c r="D254" s="13"/>
@@ -7921,9 +7789,7 @@
       <c r="N254" s="16"/>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A255" s="8">
-        <v>46494</v>
-      </c>
+      <c r="A255" s="8"/>
       <c r="B255" s="13"/>
       <c r="C255" s="13"/>
       <c r="D255" s="13"/>
@@ -7945,9 +7811,7 @@
       <c r="N255" s="16"/>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A256" s="8">
-        <v>46495</v>
-      </c>
+      <c r="A256" s="8"/>
       <c r="B256" s="13"/>
       <c r="C256" s="13"/>
       <c r="D256" s="13"/>
@@ -7969,9 +7833,7 @@
       <c r="N256" s="16"/>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A257" s="8">
-        <v>46496</v>
-      </c>
+      <c r="A257" s="8"/>
       <c r="B257" s="13"/>
       <c r="C257" s="13"/>
       <c r="D257" s="13"/>
@@ -7993,9 +7855,7 @@
       <c r="N257" s="16"/>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A258" s="8">
-        <v>46497</v>
-      </c>
+      <c r="A258" s="8"/>
       <c r="B258" s="13"/>
       <c r="C258" s="13"/>
       <c r="D258" s="13"/>
@@ -8017,9 +7877,7 @@
       <c r="N258" s="16"/>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A259" s="8">
-        <v>46498</v>
-      </c>
+      <c r="A259" s="8"/>
       <c r="B259" s="13"/>
       <c r="C259" s="13"/>
       <c r="D259" s="13"/>
@@ -8041,9 +7899,7 @@
       <c r="N259" s="16"/>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A260" s="8">
-        <v>46499</v>
-      </c>
+      <c r="A260" s="8"/>
       <c r="B260" s="13"/>
       <c r="C260" s="13"/>
       <c r="D260" s="13"/>
@@ -8065,9 +7921,7 @@
       <c r="N260" s="16"/>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A261" s="8">
-        <v>46500</v>
-      </c>
+      <c r="A261" s="8"/>
       <c r="B261" s="13"/>
       <c r="C261" s="13"/>
       <c r="D261" s="13"/>
@@ -8089,9 +7943,7 @@
       <c r="N261" s="16"/>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A262" s="8">
-        <v>46501</v>
-      </c>
+      <c r="A262" s="8"/>
       <c r="B262" s="13"/>
       <c r="C262" s="13"/>
       <c r="D262" s="13"/>
@@ -8113,9 +7965,7 @@
       <c r="N262" s="16"/>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A263" s="8">
-        <v>46502</v>
-      </c>
+      <c r="A263" s="8"/>
       <c r="B263" s="13"/>
       <c r="C263" s="13"/>
       <c r="D263" s="13"/>
@@ -8137,9 +7987,7 @@
       <c r="N263" s="16"/>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A264" s="8">
-        <v>46503</v>
-      </c>
+      <c r="A264" s="8"/>
       <c r="B264" s="13"/>
       <c r="C264" s="13"/>
       <c r="D264" s="13"/>
@@ -8161,9 +8009,7 @@
       <c r="N264" s="16"/>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A265" s="8">
-        <v>46504</v>
-      </c>
+      <c r="A265" s="8"/>
       <c r="B265" s="13"/>
       <c r="C265" s="13"/>
       <c r="D265" s="13"/>
@@ -8185,9 +8031,7 @@
       <c r="N265" s="16"/>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A266" s="8">
-        <v>46505</v>
-      </c>
+      <c r="A266" s="8"/>
       <c r="B266" s="13"/>
       <c r="C266" s="13"/>
       <c r="D266" s="13"/>
@@ -8209,9 +8053,7 @@
       <c r="N266" s="16"/>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A267" s="8">
-        <v>46506</v>
-      </c>
+      <c r="A267" s="8"/>
       <c r="B267" s="13"/>
       <c r="C267" s="13"/>
       <c r="D267" s="13"/>
@@ -8233,9 +8075,7 @@
       <c r="N267" s="16"/>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A268" s="8">
-        <v>46507</v>
-      </c>
+      <c r="A268" s="8"/>
       <c r="B268" s="13"/>
       <c r="C268" s="13"/>
       <c r="D268" s="13"/>
@@ -8257,9 +8097,7 @@
       <c r="N268" s="16"/>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A269" s="8">
-        <v>46508</v>
-      </c>
+      <c r="A269" s="8"/>
       <c r="B269" s="13"/>
       <c r="C269" s="13"/>
       <c r="D269" s="13"/>
@@ -8281,9 +8119,7 @@
       <c r="N269" s="16"/>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A270" s="8">
-        <v>46509</v>
-      </c>
+      <c r="A270" s="8"/>
       <c r="B270" s="13"/>
       <c r="C270" s="13"/>
       <c r="D270" s="13"/>
@@ -8305,9 +8141,7 @@
       <c r="N270" s="16"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A271" s="8">
-        <v>46510</v>
-      </c>
+      <c r="A271" s="8"/>
       <c r="B271" s="13"/>
       <c r="C271" s="13"/>
       <c r="D271" s="13"/>
@@ -8329,9 +8163,7 @@
       <c r="N271" s="16"/>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A272" s="8">
-        <v>46511</v>
-      </c>
+      <c r="A272" s="8"/>
       <c r="B272" s="13"/>
       <c r="C272" s="13"/>
       <c r="D272" s="13"/>
@@ -8353,9 +8185,7 @@
       <c r="N272" s="16"/>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A273" s="8">
-        <v>46512</v>
-      </c>
+      <c r="A273" s="8"/>
       <c r="B273" s="13"/>
       <c r="C273" s="13"/>
       <c r="D273" s="13"/>
@@ -8377,9 +8207,7 @@
       <c r="N273" s="16"/>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A274" s="8">
-        <v>46513</v>
-      </c>
+      <c r="A274" s="8"/>
       <c r="B274" s="13"/>
       <c r="C274" s="13"/>
       <c r="D274" s="13"/>
@@ -8401,9 +8229,7 @@
       <c r="N274" s="16"/>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A275" s="8">
-        <v>46514</v>
-      </c>
+      <c r="A275" s="8"/>
       <c r="B275" s="13"/>
       <c r="C275" s="13"/>
       <c r="D275" s="13"/>
@@ -8425,9 +8251,7 @@
       <c r="N275" s="16"/>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A276" s="8">
-        <v>46515</v>
-      </c>
+      <c r="A276" s="8"/>
       <c r="B276" s="13"/>
       <c r="C276" s="13"/>
       <c r="D276" s="13"/>
@@ -8449,9 +8273,7 @@
       <c r="N276" s="16"/>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A277" s="8">
-        <v>46516</v>
-      </c>
+      <c r="A277" s="8"/>
       <c r="B277" s="13"/>
       <c r="C277" s="13"/>
       <c r="D277" s="13"/>
@@ -8473,9 +8295,7 @@
       <c r="N277" s="16"/>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A278" s="8">
-        <v>46517</v>
-      </c>
+      <c r="A278" s="8"/>
       <c r="B278" s="13"/>
       <c r="C278" s="13"/>
       <c r="D278" s="13"/>
@@ -8497,9 +8317,7 @@
       <c r="N278" s="16"/>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A279" s="8">
-        <v>46518</v>
-      </c>
+      <c r="A279" s="8"/>
       <c r="B279" s="13"/>
       <c r="C279" s="13"/>
       <c r="D279" s="13"/>
@@ -8521,9 +8339,7 @@
       <c r="N279" s="16"/>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A280" s="8">
-        <v>46519</v>
-      </c>
+      <c r="A280" s="8"/>
       <c r="B280" s="13"/>
       <c r="C280" s="13"/>
       <c r="D280" s="13"/>
@@ -8545,9 +8361,7 @@
       <c r="N280" s="16"/>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A281" s="8">
-        <v>46520</v>
-      </c>
+      <c r="A281" s="8"/>
       <c r="B281" s="13"/>
       <c r="C281" s="13"/>
       <c r="D281" s="13"/>
@@ -8569,9 +8383,7 @@
       <c r="N281" s="16"/>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A282" s="8">
-        <v>46521</v>
-      </c>
+      <c r="A282" s="8"/>
       <c r="B282" s="13"/>
       <c r="C282" s="13"/>
       <c r="D282" s="13"/>
@@ -8593,9 +8405,7 @@
       <c r="N282" s="16"/>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A283" s="8">
-        <v>46522</v>
-      </c>
+      <c r="A283" s="8"/>
       <c r="B283" s="13"/>
       <c r="C283" s="13"/>
       <c r="D283" s="13"/>
@@ -8617,9 +8427,7 @@
       <c r="N283" s="16"/>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A284" s="8">
-        <v>46523</v>
-      </c>
+      <c r="A284" s="8"/>
       <c r="B284" s="13"/>
       <c r="C284" s="13"/>
       <c r="D284" s="13"/>
@@ -8641,9 +8449,7 @@
       <c r="N284" s="16"/>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A285" s="8">
-        <v>46524</v>
-      </c>
+      <c r="A285" s="8"/>
       <c r="B285" s="13"/>
       <c r="C285" s="13"/>
       <c r="D285" s="13"/>
@@ -8665,9 +8471,7 @@
       <c r="N285" s="16"/>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A286" s="8">
-        <v>46525</v>
-      </c>
+      <c r="A286" s="8"/>
       <c r="B286" s="13"/>
       <c r="C286" s="13"/>
       <c r="D286" s="13"/>
@@ -8689,9 +8493,7 @@
       <c r="N286" s="16"/>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A287" s="8">
-        <v>46526</v>
-      </c>
+      <c r="A287" s="8"/>
       <c r="B287" s="13"/>
       <c r="C287" s="13"/>
       <c r="D287" s="13"/>
@@ -8713,9 +8515,7 @@
       <c r="N287" s="16"/>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A288" s="8">
-        <v>46527</v>
-      </c>
+      <c r="A288" s="8"/>
       <c r="B288" s="13"/>
       <c r="C288" s="13"/>
       <c r="D288" s="13"/>
@@ -8737,9 +8537,7 @@
       <c r="N288" s="16"/>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A289" s="8">
-        <v>46528</v>
-      </c>
+      <c r="A289" s="8"/>
       <c r="B289" s="13"/>
       <c r="C289" s="13"/>
       <c r="D289" s="13"/>
@@ -8761,9 +8559,7 @@
       <c r="N289" s="16"/>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A290" s="8">
-        <v>46529</v>
-      </c>
+      <c r="A290" s="8"/>
       <c r="B290" s="13"/>
       <c r="C290" s="13"/>
       <c r="D290" s="13"/>
@@ -8785,9 +8581,7 @@
       <c r="N290" s="16"/>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A291" s="8">
-        <v>46530</v>
-      </c>
+      <c r="A291" s="8"/>
       <c r="B291" s="13"/>
       <c r="C291" s="13"/>
       <c r="D291" s="13"/>
@@ -8809,9 +8603,7 @@
       <c r="N291" s="16"/>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A292" s="8">
-        <v>46531</v>
-      </c>
+      <c r="A292" s="8"/>
       <c r="B292" s="13"/>
       <c r="C292" s="13"/>
       <c r="D292" s="13"/>
@@ -8833,9 +8625,7 @@
       <c r="N292" s="16"/>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A293" s="8">
-        <v>46532</v>
-      </c>
+      <c r="A293" s="8"/>
       <c r="B293" s="13"/>
       <c r="C293" s="13"/>
       <c r="D293" s="13"/>
@@ -8857,9 +8647,7 @@
       <c r="N293" s="16"/>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A294" s="8">
-        <v>46533</v>
-      </c>
+      <c r="A294" s="8"/>
       <c r="B294" s="13"/>
       <c r="C294" s="13"/>
       <c r="D294" s="13"/>
@@ -8881,9 +8669,7 @@
       <c r="N294" s="16"/>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A295" s="8">
-        <v>46534</v>
-      </c>
+      <c r="A295" s="8"/>
       <c r="B295" s="13"/>
       <c r="C295" s="13"/>
       <c r="D295" s="13"/>
@@ -8905,9 +8691,7 @@
       <c r="N295" s="16"/>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A296" s="8">
-        <v>46535</v>
-      </c>
+      <c r="A296" s="8"/>
       <c r="B296" s="13"/>
       <c r="C296" s="13"/>
       <c r="D296" s="13"/>
@@ -8929,9 +8713,7 @@
       <c r="N296" s="16"/>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A297" s="8">
-        <v>46536</v>
-      </c>
+      <c r="A297" s="8"/>
       <c r="B297" s="13"/>
       <c r="C297" s="13"/>
       <c r="D297" s="13"/>
@@ -8953,9 +8735,7 @@
       <c r="N297" s="16"/>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A298" s="8">
-        <v>46537</v>
-      </c>
+      <c r="A298" s="8"/>
       <c r="B298" s="13"/>
       <c r="C298" s="13"/>
       <c r="D298" s="13"/>
@@ -8977,9 +8757,7 @@
       <c r="N298" s="16"/>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A299" s="8">
-        <v>46538</v>
-      </c>
+      <c r="A299" s="8"/>
       <c r="B299" s="13"/>
       <c r="C299" s="13"/>
       <c r="D299" s="13"/>
@@ -9001,9 +8779,7 @@
       <c r="N299" s="16"/>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A300" s="8">
-        <v>46539</v>
-      </c>
+      <c r="A300" s="8"/>
       <c r="B300" s="13"/>
       <c r="C300" s="13"/>
       <c r="D300" s="13"/>
@@ -9025,9 +8801,7 @@
       <c r="N300" s="16"/>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A301" s="8">
-        <v>46540</v>
-      </c>
+      <c r="A301" s="8"/>
       <c r="B301" s="13"/>
       <c r="C301" s="13"/>
       <c r="D301" s="13"/>
@@ -9049,9 +8823,7 @@
       <c r="N301" s="16"/>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A302" s="8">
-        <v>46541</v>
-      </c>
+      <c r="A302" s="8"/>
       <c r="B302" s="13"/>
       <c r="C302" s="13"/>
       <c r="D302" s="13"/>
@@ -9073,9 +8845,7 @@
       <c r="N302" s="16"/>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A303" s="8">
-        <v>46542</v>
-      </c>
+      <c r="A303" s="8"/>
       <c r="B303" s="13"/>
       <c r="C303" s="13"/>
       <c r="D303" s="13"/>
@@ -9097,9 +8867,7 @@
       <c r="N303" s="16"/>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A304" s="8">
-        <v>46543</v>
-      </c>
+      <c r="A304" s="8"/>
       <c r="B304" s="13"/>
       <c r="C304" s="13"/>
       <c r="D304" s="13"/>
@@ -9121,9 +8889,7 @@
       <c r="N304" s="16"/>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A305" s="8">
-        <v>46544</v>
-      </c>
+      <c r="A305" s="8"/>
       <c r="B305" s="13"/>
       <c r="C305" s="13"/>
       <c r="D305" s="13"/>
@@ -9145,9 +8911,7 @@
       <c r="N305" s="16"/>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A306" s="8">
-        <v>46545</v>
-      </c>
+      <c r="A306" s="8"/>
       <c r="B306" s="13"/>
       <c r="C306" s="13"/>
       <c r="D306" s="13"/>
@@ -9169,9 +8933,7 @@
       <c r="N306" s="16"/>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A307" s="8">
-        <v>46546</v>
-      </c>
+      <c r="A307" s="8"/>
       <c r="B307" s="13"/>
       <c r="C307" s="13"/>
       <c r="D307" s="13"/>
@@ -9193,9 +8955,7 @@
       <c r="N307" s="16"/>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A308" s="8">
-        <v>46547</v>
-      </c>
+      <c r="A308" s="8"/>
       <c r="B308" s="13"/>
       <c r="C308" s="13"/>
       <c r="D308" s="13"/>
@@ -9217,9 +8977,7 @@
       <c r="N308" s="16"/>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A309" s="8">
-        <v>46548</v>
-      </c>
+      <c r="A309" s="8"/>
       <c r="B309" s="13"/>
       <c r="C309" s="13"/>
       <c r="D309" s="13"/>
@@ -9241,9 +8999,7 @@
       <c r="N309" s="16"/>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A310" s="8">
-        <v>46549</v>
-      </c>
+      <c r="A310" s="8"/>
       <c r="B310" s="13"/>
       <c r="C310" s="13"/>
       <c r="D310" s="13"/>
@@ -9265,9 +9021,7 @@
       <c r="N310" s="16"/>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A311" s="8">
-        <v>46550</v>
-      </c>
+      <c r="A311" s="8"/>
       <c r="B311" s="13"/>
       <c r="C311" s="13"/>
       <c r="D311" s="13"/>
@@ -9289,9 +9043,7 @@
       <c r="N311" s="16"/>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A312" s="8">
-        <v>46551</v>
-      </c>
+      <c r="A312" s="8"/>
       <c r="B312" s="13"/>
       <c r="C312" s="13"/>
       <c r="D312" s="13"/>
@@ -9313,9 +9065,7 @@
       <c r="N312" s="16"/>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A313" s="8">
-        <v>46552</v>
-      </c>
+      <c r="A313" s="8"/>
       <c r="B313" s="13"/>
       <c r="C313" s="13"/>
       <c r="D313" s="13"/>
@@ -9337,9 +9087,7 @@
       <c r="N313" s="16"/>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A314" s="8">
-        <v>46553</v>
-      </c>
+      <c r="A314" s="8"/>
       <c r="B314" s="13"/>
       <c r="C314" s="13"/>
       <c r="D314" s="13"/>
@@ -9361,9 +9109,7 @@
       <c r="N314" s="16"/>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A315" s="8">
-        <v>46554</v>
-      </c>
+      <c r="A315" s="8"/>
       <c r="B315" s="13"/>
       <c r="C315" s="13"/>
       <c r="D315" s="13"/>
@@ -9385,9 +9131,7 @@
       <c r="N315" s="16"/>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A316" s="8">
-        <v>46555</v>
-      </c>
+      <c r="A316" s="8"/>
       <c r="B316" s="13"/>
       <c r="C316" s="13"/>
       <c r="D316" s="13"/>
@@ -9409,9 +9153,7 @@
       <c r="N316" s="16"/>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A317" s="8">
-        <v>46556</v>
-      </c>
+      <c r="A317" s="8"/>
       <c r="B317" s="13"/>
       <c r="C317" s="13"/>
       <c r="D317" s="13"/>
@@ -9433,9 +9175,7 @@
       <c r="N317" s="16"/>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A318" s="8">
-        <v>46557</v>
-      </c>
+      <c r="A318" s="8"/>
       <c r="B318" s="13"/>
       <c r="C318" s="13"/>
       <c r="D318" s="13"/>
@@ -9457,9 +9197,7 @@
       <c r="N318" s="16"/>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A319" s="8">
-        <v>46558</v>
-      </c>
+      <c r="A319" s="8"/>
       <c r="B319" s="13"/>
       <c r="C319" s="13"/>
       <c r="D319" s="13"/>
@@ -9481,9 +9219,7 @@
       <c r="N319" s="16"/>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A320" s="8">
-        <v>46559</v>
-      </c>
+      <c r="A320" s="8"/>
       <c r="B320" s="13"/>
       <c r="C320" s="13"/>
       <c r="D320" s="13"/>
@@ -9505,9 +9241,7 @@
       <c r="N320" s="16"/>
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A321" s="8">
-        <v>46560</v>
-      </c>
+      <c r="A321" s="8"/>
       <c r="B321" s="13"/>
       <c r="C321" s="13"/>
       <c r="D321" s="13"/>
@@ -9529,9 +9263,7 @@
       <c r="N321" s="16"/>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A322" s="8">
-        <v>46561</v>
-      </c>
+      <c r="A322" s="8"/>
       <c r="B322" s="13"/>
       <c r="C322" s="13"/>
       <c r="D322" s="13"/>
@@ -9553,9 +9285,7 @@
       <c r="N322" s="16"/>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A323" s="8">
-        <v>46562</v>
-      </c>
+      <c r="A323" s="8"/>
       <c r="B323" s="13"/>
       <c r="C323" s="13"/>
       <c r="D323" s="13"/>
@@ -9577,9 +9307,7 @@
       <c r="N323" s="16"/>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A324" s="8">
-        <v>46563</v>
-      </c>
+      <c r="A324" s="8"/>
       <c r="B324" s="13"/>
       <c r="C324" s="13"/>
       <c r="D324" s="13"/>
@@ -9601,9 +9329,7 @@
       <c r="N324" s="16"/>
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A325" s="8">
-        <v>46564</v>
-      </c>
+      <c r="A325" s="8"/>
       <c r="B325" s="13"/>
       <c r="C325" s="13"/>
       <c r="D325" s="13"/>
@@ -9625,9 +9351,7 @@
       <c r="N325" s="16"/>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A326" s="8">
-        <v>46565</v>
-      </c>
+      <c r="A326" s="8"/>
       <c r="B326" s="13"/>
       <c r="C326" s="13"/>
       <c r="D326" s="13"/>
@@ -9649,9 +9373,7 @@
       <c r="N326" s="16"/>
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A327" s="8">
-        <v>46566</v>
-      </c>
+      <c r="A327" s="8"/>
       <c r="B327" s="13"/>
       <c r="C327" s="13"/>
       <c r="D327" s="13"/>
@@ -9673,9 +9395,7 @@
       <c r="N327" s="16"/>
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A328" s="8">
-        <v>46567</v>
-      </c>
+      <c r="A328" s="8"/>
       <c r="B328" s="13"/>
       <c r="C328" s="13"/>
       <c r="D328" s="13"/>
@@ -9697,9 +9417,7 @@
       <c r="N328" s="16"/>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A329" s="8">
-        <v>46568</v>
-      </c>
+      <c r="A329" s="8"/>
       <c r="B329" s="13"/>
       <c r="C329" s="13"/>
       <c r="D329" s="13"/>
@@ -9721,9 +9439,7 @@
       <c r="N329" s="16"/>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A330" s="8">
-        <v>46569</v>
-      </c>
+      <c r="A330" s="8"/>
       <c r="B330" s="13"/>
       <c r="C330" s="13"/>
       <c r="D330" s="13"/>
@@ -9745,9 +9461,7 @@
       <c r="N330" s="16"/>
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A331" s="8">
-        <v>46570</v>
-      </c>
+      <c r="A331" s="8"/>
       <c r="B331" s="13"/>
       <c r="C331" s="13"/>
       <c r="D331" s="13"/>
@@ -9769,9 +9483,7 @@
       <c r="N331" s="16"/>
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A332" s="8">
-        <v>46571</v>
-      </c>
+      <c r="A332" s="8"/>
       <c r="B332" s="13"/>
       <c r="C332" s="13"/>
       <c r="D332" s="13"/>
@@ -9793,9 +9505,7 @@
       <c r="N332" s="16"/>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A333" s="8">
-        <v>46572</v>
-      </c>
+      <c r="A333" s="8"/>
       <c r="B333" s="13"/>
       <c r="C333" s="13"/>
       <c r="D333" s="13"/>
@@ -9817,9 +9527,7 @@
       <c r="N333" s="16"/>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A334" s="8">
-        <v>46573</v>
-      </c>
+      <c r="A334" s="8"/>
       <c r="B334" s="13"/>
       <c r="C334" s="13"/>
       <c r="D334" s="13"/>
@@ -9841,9 +9549,7 @@
       <c r="N334" s="16"/>
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A335" s="8">
-        <v>46574</v>
-      </c>
+      <c r="A335" s="8"/>
       <c r="B335" s="13"/>
       <c r="C335" s="13"/>
       <c r="D335" s="13"/>
@@ -9865,9 +9571,7 @@
       <c r="N335" s="16"/>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A336" s="8">
-        <v>46575</v>
-      </c>
+      <c r="A336" s="8"/>
       <c r="B336" s="13"/>
       <c r="C336" s="13"/>
       <c r="D336" s="13"/>
@@ -9889,9 +9593,7 @@
       <c r="N336" s="16"/>
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A337" s="8">
-        <v>46576</v>
-      </c>
+      <c r="A337" s="8"/>
       <c r="B337" s="13"/>
       <c r="C337" s="13"/>
       <c r="D337" s="13"/>
@@ -9913,9 +9615,7 @@
       <c r="N337" s="16"/>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A338" s="8">
-        <v>46577</v>
-      </c>
+      <c r="A338" s="8"/>
       <c r="B338" s="13"/>
       <c r="C338" s="13"/>
       <c r="D338" s="13"/>
@@ -9937,9 +9637,7 @@
       <c r="N338" s="16"/>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A339" s="8">
-        <v>46578</v>
-      </c>
+      <c r="A339" s="8"/>
       <c r="B339" s="13"/>
       <c r="C339" s="13"/>
       <c r="D339" s="13"/>
@@ -9961,9 +9659,7 @@
       <c r="N339" s="16"/>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A340" s="8">
-        <v>46579</v>
-      </c>
+      <c r="A340" s="8"/>
       <c r="B340" s="13"/>
       <c r="C340" s="13"/>
       <c r="D340" s="13"/>
@@ -9985,9 +9681,7 @@
       <c r="N340" s="16"/>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A341" s="8">
-        <v>46580</v>
-      </c>
+      <c r="A341" s="8"/>
       <c r="B341" s="13"/>
       <c r="C341" s="13"/>
       <c r="D341" s="13"/>
@@ -10009,9 +9703,7 @@
       <c r="N341" s="16"/>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A342" s="8">
-        <v>46581</v>
-      </c>
+      <c r="A342" s="8"/>
       <c r="B342" s="13"/>
       <c r="C342" s="13"/>
       <c r="D342" s="13"/>
@@ -10033,9 +9725,7 @@
       <c r="N342" s="16"/>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A343" s="8">
-        <v>46582</v>
-      </c>
+      <c r="A343" s="8"/>
       <c r="B343" s="13"/>
       <c r="C343" s="13"/>
       <c r="D343" s="13"/>
@@ -10057,9 +9747,7 @@
       <c r="N343" s="16"/>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A344" s="8">
-        <v>46583</v>
-      </c>
+      <c r="A344" s="8"/>
       <c r="B344" s="13"/>
       <c r="C344" s="13"/>
       <c r="D344" s="13"/>
@@ -10081,9 +9769,7 @@
       <c r="N344" s="16"/>
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A345" s="8">
-        <v>46584</v>
-      </c>
+      <c r="A345" s="8"/>
       <c r="B345" s="13"/>
       <c r="C345" s="13"/>
       <c r="D345" s="13"/>
@@ -10105,9 +9791,7 @@
       <c r="N345" s="16"/>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A346" s="8">
-        <v>46585</v>
-      </c>
+      <c r="A346" s="8"/>
       <c r="B346" s="13"/>
       <c r="C346" s="13"/>
       <c r="D346" s="13"/>
@@ -10129,9 +9813,7 @@
       <c r="N346" s="16"/>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A347" s="8">
-        <v>46586</v>
-      </c>
+      <c r="A347" s="8"/>
       <c r="B347" s="13"/>
       <c r="C347" s="13"/>
       <c r="D347" s="13"/>
@@ -10153,9 +9835,7 @@
       <c r="N347" s="16"/>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A348" s="8">
-        <v>46587</v>
-      </c>
+      <c r="A348" s="8"/>
       <c r="B348" s="13"/>
       <c r="C348" s="13"/>
       <c r="D348" s="13"/>
@@ -10177,9 +9857,7 @@
       <c r="N348" s="16"/>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A349" s="8">
-        <v>46588</v>
-      </c>
+      <c r="A349" s="8"/>
       <c r="B349" s="13"/>
       <c r="C349" s="13"/>
       <c r="D349" s="13"/>
@@ -10201,9 +9879,7 @@
       <c r="N349" s="16"/>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A350" s="8">
-        <v>46589</v>
-      </c>
+      <c r="A350" s="8"/>
       <c r="B350" s="13"/>
       <c r="C350" s="13"/>
       <c r="D350" s="13"/>
@@ -10225,9 +9901,7 @@
       <c r="N350" s="16"/>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A351" s="8">
-        <v>46590</v>
-      </c>
+      <c r="A351" s="8"/>
       <c r="B351" s="13"/>
       <c r="C351" s="13"/>
       <c r="D351" s="13"/>
@@ -10249,9 +9923,7 @@
       <c r="N351" s="16"/>
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A352" s="8">
-        <v>46591</v>
-      </c>
+      <c r="A352" s="8"/>
       <c r="B352" s="13"/>
       <c r="C352" s="13"/>
       <c r="D352" s="13"/>
@@ -10273,9 +9945,7 @@
       <c r="N352" s="16"/>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A353" s="8">
-        <v>46592</v>
-      </c>
+      <c r="A353" s="8"/>
       <c r="B353" s="13"/>
       <c r="C353" s="13"/>
       <c r="D353" s="13"/>
@@ -10297,9 +9967,7 @@
       <c r="N353" s="16"/>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A354" s="8">
-        <v>46593</v>
-      </c>
+      <c r="A354" s="8"/>
       <c r="B354" s="13"/>
       <c r="C354" s="13"/>
       <c r="D354" s="13"/>
@@ -10321,9 +9989,7 @@
       <c r="N354" s="16"/>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A355" s="8">
-        <v>46594</v>
-      </c>
+      <c r="A355" s="8"/>
       <c r="B355" s="13"/>
       <c r="C355" s="13"/>
       <c r="D355" s="13"/>
@@ -10345,9 +10011,7 @@
       <c r="N355" s="16"/>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A356" s="8">
-        <v>46595</v>
-      </c>
+      <c r="A356" s="8"/>
       <c r="B356" s="13"/>
       <c r="C356" s="13"/>
       <c r="D356" s="13"/>
@@ -10369,9 +10033,7 @@
       <c r="N356" s="16"/>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A357" s="8">
-        <v>46596</v>
-      </c>
+      <c r="A357" s="8"/>
       <c r="B357" s="13"/>
       <c r="C357" s="13"/>
       <c r="D357" s="13"/>
@@ -10393,9 +10055,7 @@
       <c r="N357" s="16"/>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A358" s="8">
-        <v>46597</v>
-      </c>
+      <c r="A358" s="8"/>
       <c r="B358" s="13"/>
       <c r="C358" s="13"/>
       <c r="D358" s="13"/>
@@ -10417,9 +10077,7 @@
       <c r="N358" s="16"/>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A359" s="8">
-        <v>46598</v>
-      </c>
+      <c r="A359" s="8"/>
       <c r="B359" s="13"/>
       <c r="C359" s="13"/>
       <c r="D359" s="13"/>
@@ -10441,9 +10099,7 @@
       <c r="N359" s="16"/>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A360" s="8">
-        <v>46599</v>
-      </c>
+      <c r="A360" s="8"/>
       <c r="B360" s="13"/>
       <c r="C360" s="13"/>
       <c r="D360" s="13"/>
@@ -10465,9 +10121,7 @@
       <c r="N360" s="16"/>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A361" s="8">
-        <v>46600</v>
-      </c>
+      <c r="A361" s="8"/>
       <c r="B361" s="13"/>
       <c r="C361" s="13"/>
       <c r="D361" s="13"/>
@@ -10489,9 +10143,7 @@
       <c r="N361" s="16"/>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A362" s="8">
-        <v>46601</v>
-      </c>
+      <c r="A362" s="8"/>
       <c r="B362" s="13"/>
       <c r="C362" s="13"/>
       <c r="D362" s="13"/>
@@ -10513,9 +10165,7 @@
       <c r="N362" s="16"/>
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A363" s="8">
-        <v>46602</v>
-      </c>
+      <c r="A363" s="8"/>
       <c r="B363" s="13"/>
       <c r="C363" s="13"/>
       <c r="D363" s="13"/>
@@ -10537,9 +10187,7 @@
       <c r="N363" s="16"/>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A364" s="8">
-        <v>46603</v>
-      </c>
+      <c r="A364" s="8"/>
       <c r="B364" s="13"/>
       <c r="C364" s="13"/>
       <c r="D364" s="13"/>
@@ -10561,9 +10209,7 @@
       <c r="N364" s="16"/>
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A365" s="8">
-        <v>46604</v>
-      </c>
+      <c r="A365" s="8"/>
       <c r="B365" s="13"/>
       <c r="C365" s="13"/>
       <c r="D365" s="13"/>
@@ -10585,9 +10231,7 @@
       <c r="N365" s="16"/>
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A366" s="8">
-        <v>46605</v>
-      </c>
+      <c r="A366" s="8"/>
       <c r="B366" s="13"/>
       <c r="C366" s="13"/>
       <c r="D366" s="13"/>
@@ -10609,9 +10253,7 @@
       <c r="N366" s="16"/>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A367" s="8">
-        <v>46606</v>
-      </c>
+      <c r="A367" s="8"/>
       <c r="B367" s="13"/>
       <c r="C367" s="13"/>
       <c r="D367" s="13"/>
@@ -10633,9 +10275,7 @@
       <c r="N367" s="16"/>
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A368" s="8">
-        <v>46607</v>
-      </c>
+      <c r="A368" s="8"/>
       <c r="B368" s="13"/>
       <c r="C368" s="13"/>
       <c r="D368" s="13"/>
@@ -10657,9 +10297,7 @@
       <c r="N368" s="16"/>
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A369" s="8">
-        <v>46608</v>
-      </c>
+      <c r="A369" s="8"/>
       <c r="B369" s="13"/>
       <c r="C369" s="13"/>
       <c r="D369" s="13"/>
@@ -10681,9 +10319,7 @@
       <c r="N369" s="16"/>
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A370" s="8">
-        <v>46609</v>
-      </c>
+      <c r="A370" s="8"/>
       <c r="B370" s="13"/>
       <c r="C370" s="13"/>
       <c r="D370" s="13"/>
@@ -10705,9 +10341,7 @@
       <c r="N370" s="16"/>
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A371" s="8">
-        <v>46610</v>
-      </c>
+      <c r="A371" s="8"/>
       <c r="B371" s="13"/>
       <c r="C371" s="13"/>
       <c r="D371" s="13"/>
@@ -10729,9 +10363,7 @@
       <c r="N371" s="16"/>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A372" s="8">
-        <v>46611</v>
-      </c>
+      <c r="A372" s="8"/>
       <c r="B372" s="13"/>
       <c r="C372" s="13"/>
       <c r="D372" s="13"/>
@@ -10753,9 +10385,7 @@
       <c r="N372" s="16"/>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A373" s="8">
-        <v>46612</v>
-      </c>
+      <c r="A373" s="8"/>
       <c r="B373" s="13"/>
       <c r="C373" s="13"/>
       <c r="D373" s="13"/>
@@ -10777,9 +10407,7 @@
       <c r="N373" s="16"/>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A374" s="8">
-        <v>46613</v>
-      </c>
+      <c r="A374" s="8"/>
       <c r="B374" s="13"/>
       <c r="C374" s="13"/>
       <c r="D374" s="13"/>
@@ -10801,9 +10429,7 @@
       <c r="N374" s="16"/>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A375" s="8">
-        <v>46614</v>
-      </c>
+      <c r="A375" s="8"/>
       <c r="B375" s="13"/>
       <c r="C375" s="13"/>
       <c r="D375" s="13"/>
@@ -10825,9 +10451,7 @@
       <c r="N375" s="16"/>
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A376" s="8">
-        <v>46615</v>
-      </c>
+      <c r="A376" s="8"/>
       <c r="B376" s="13"/>
       <c r="C376" s="13"/>
       <c r="D376" s="13"/>
@@ -10849,9 +10473,7 @@
       <c r="N376" s="16"/>
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A377" s="8">
-        <v>46616</v>
-      </c>
+      <c r="A377" s="8"/>
       <c r="B377" s="13"/>
       <c r="C377" s="13"/>
       <c r="D377" s="13"/>
@@ -10873,9 +10495,7 @@
       <c r="N377" s="16"/>
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A378" s="8">
-        <v>46617</v>
-      </c>
+      <c r="A378" s="8"/>
       <c r="B378" s="13"/>
       <c r="C378" s="13"/>
       <c r="D378" s="13"/>
@@ -10897,9 +10517,7 @@
       <c r="N378" s="16"/>
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A379" s="8">
-        <v>46618</v>
-      </c>
+      <c r="A379" s="8"/>
       <c r="B379" s="13"/>
       <c r="C379" s="13"/>
       <c r="D379" s="13"/>
@@ -10921,9 +10539,7 @@
       <c r="N379" s="16"/>
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A380" s="8">
-        <v>46619</v>
-      </c>
+      <c r="A380" s="8"/>
       <c r="B380" s="13"/>
       <c r="C380" s="13"/>
       <c r="D380" s="13"/>
@@ -10945,9 +10561,7 @@
       <c r="N380" s="16"/>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A381" s="8">
-        <v>46620</v>
-      </c>
+      <c r="A381" s="8"/>
       <c r="B381" s="13"/>
       <c r="C381" s="13"/>
       <c r="D381" s="13"/>
@@ -10969,9 +10583,7 @@
       <c r="N381" s="16"/>
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A382" s="8">
-        <v>46621</v>
-      </c>
+      <c r="A382" s="8"/>
       <c r="B382" s="13"/>
       <c r="C382" s="13"/>
       <c r="D382" s="13"/>
@@ -10993,9 +10605,7 @@
       <c r="N382" s="16"/>
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A383" s="8">
-        <v>46622</v>
-      </c>
+      <c r="A383" s="8"/>
       <c r="B383" s="13"/>
       <c r="C383" s="13"/>
       <c r="D383" s="13"/>
@@ -11017,9 +10627,7 @@
       <c r="N383" s="16"/>
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A384" s="8">
-        <v>46623</v>
-      </c>
+      <c r="A384" s="8"/>
       <c r="B384" s="13"/>
       <c r="C384" s="13"/>
       <c r="D384" s="13"/>
@@ -11041,9 +10649,7 @@
       <c r="N384" s="16"/>
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A385" s="8">
-        <v>46624</v>
-      </c>
+      <c r="A385" s="8"/>
       <c r="B385" s="13"/>
       <c r="C385" s="13"/>
       <c r="D385" s="13"/>
@@ -11065,9 +10671,7 @@
       <c r="N385" s="16"/>
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A386" s="8">
-        <v>46625</v>
-      </c>
+      <c r="A386" s="8"/>
       <c r="B386" s="13"/>
       <c r="C386" s="13"/>
       <c r="D386" s="13"/>
@@ -11089,9 +10693,7 @@
       <c r="N386" s="16"/>
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A387" s="8">
-        <v>46626</v>
-      </c>
+      <c r="A387" s="8"/>
       <c r="B387" s="13"/>
       <c r="C387" s="13"/>
       <c r="D387" s="13"/>
@@ -11113,9 +10715,7 @@
       <c r="N387" s="16"/>
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A388" s="8">
-        <v>46627</v>
-      </c>
+      <c r="A388" s="8"/>
       <c r="B388" s="13"/>
       <c r="C388" s="13"/>
       <c r="D388" s="13"/>
@@ -11137,9 +10737,7 @@
       <c r="N388" s="16"/>
     </row>
     <row r="389" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A389" s="8">
-        <v>46628</v>
-      </c>
+      <c r="A389" s="8"/>
       <c r="B389" s="13"/>
       <c r="C389" s="13"/>
       <c r="D389" s="13"/>
@@ -11161,9 +10759,7 @@
       <c r="N389" s="16"/>
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A390" s="8">
-        <v>46629</v>
-      </c>
+      <c r="A390" s="8"/>
       <c r="B390" s="13"/>
       <c r="C390" s="13"/>
       <c r="D390" s="13"/>
@@ -11185,9 +10781,7 @@
       <c r="N390" s="16"/>
     </row>
     <row r="391" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A391" s="8">
-        <v>46630</v>
-      </c>
+      <c r="A391" s="8"/>
       <c r="B391" s="13"/>
       <c r="C391" s="13"/>
       <c r="D391" s="13"/>
@@ -11209,9 +10803,7 @@
       <c r="N391" s="16"/>
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A392" s="8">
-        <v>46631</v>
-      </c>
+      <c r="A392" s="8"/>
       <c r="B392" s="13"/>
       <c r="C392" s="13"/>
       <c r="D392" s="13"/>
@@ -11233,9 +10825,7 @@
       <c r="N392" s="16"/>
     </row>
     <row r="393" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A393" s="8">
-        <v>46632</v>
-      </c>
+      <c r="A393" s="8"/>
       <c r="B393" s="13"/>
       <c r="C393" s="13"/>
       <c r="D393" s="13"/>
@@ -11257,9 +10847,7 @@
       <c r="N393" s="16"/>
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A394" s="8">
-        <v>46633</v>
-      </c>
+      <c r="A394" s="8"/>
       <c r="B394" s="13"/>
       <c r="C394" s="13"/>
       <c r="D394" s="13"/>
@@ -11281,9 +10869,7 @@
       <c r="N394" s="16"/>
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A395" s="8">
-        <v>46634</v>
-      </c>
+      <c r="A395" s="8"/>
       <c r="B395" s="13"/>
       <c r="C395" s="13"/>
       <c r="D395" s="13"/>
@@ -11305,9 +10891,7 @@
       <c r="N395" s="16"/>
     </row>
     <row r="396" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A396" s="8">
-        <v>46635</v>
-      </c>
+      <c r="A396" s="8"/>
       <c r="B396" s="13"/>
       <c r="C396" s="13"/>
       <c r="D396" s="13"/>
@@ -11329,9 +10913,7 @@
       <c r="N396" s="16"/>
     </row>
     <row r="397" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A397" s="8">
-        <v>46636</v>
-      </c>
+      <c r="A397" s="8"/>
       <c r="B397" s="13"/>
       <c r="C397" s="13"/>
       <c r="D397" s="13"/>
@@ -11353,9 +10935,7 @@
       <c r="N397" s="16"/>
     </row>
     <row r="398" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A398" s="8">
-        <v>46637</v>
-      </c>
+      <c r="A398" s="8"/>
       <c r="B398" s="13"/>
       <c r="C398" s="13"/>
       <c r="D398" s="13"/>
@@ -11377,9 +10957,7 @@
       <c r="N398" s="16"/>
     </row>
     <row r="399" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A399" s="8">
-        <v>46638</v>
-      </c>
+      <c r="A399" s="8"/>
       <c r="B399" s="13"/>
       <c r="C399" s="13"/>
       <c r="D399" s="13"/>
@@ -11401,9 +10979,7 @@
       <c r="N399" s="16"/>
     </row>
     <row r="400" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A400" s="8">
-        <v>46639</v>
-      </c>
+      <c r="A400" s="8"/>
       <c r="B400" s="13"/>
       <c r="C400" s="13"/>
       <c r="D400" s="13"/>
@@ -11425,9 +11001,7 @@
       <c r="N400" s="16"/>
     </row>
     <row r="401" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A401" s="8">
-        <v>46640</v>
-      </c>
+      <c r="A401" s="8"/>
       <c r="B401" s="13"/>
       <c r="C401" s="13"/>
       <c r="D401" s="13"/>
@@ -11447,6 +11021,9 @@
       <c r="L401" s="15"/>
       <c r="M401" s="15"/>
       <c r="N401" s="16"/>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A402" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/12608100.xlsx
+++ b/12608100.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/178e7b8b65df52d4/Desktop/CAP-776/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="949" documentId="8_{423A2F30-43C3-4C4F-AB9B-22B4BC24882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87AD7CBD-FA53-467A-8559-122BA4EAA954}"/>
+  <xr:revisionPtr revIDLastSave="984" documentId="8_{423A2F30-43C3-4C4F-AB9B-22B4BC24882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B3AFDCA-0E72-47D4-ADDE-477B1BF45547}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="125">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -401,6 +401,15 @@
   </si>
   <si>
     <t>really needed a weekend, uff.</t>
+  </si>
+  <si>
+    <t>Saturday, and I want to sleep more</t>
+  </si>
+  <si>
+    <t>first time I went for solo outing. Felt a little awkward but then I enjoyed my own company</t>
+  </si>
+  <si>
+    <t>it's a holiday.</t>
   </si>
 </sst>
 </file>
@@ -4337,7 +4346,7 @@
         <v>46315</v>
       </c>
       <c r="B74" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="C74" s="9">
         <v>60</v>
@@ -4359,11 +4368,11 @@
       </c>
       <c r="I74" s="10">
         <f t="shared" si="2"/>
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="J74" s="10">
         <f t="shared" si="3"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>60</v>
@@ -4516,77 +4525,143 @@
         <v>121</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>46319</v>
       </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="10" t="str">
+      <c r="B78" s="9">
+        <v>540</v>
+      </c>
+      <c r="C78" s="9">
+        <v>30</v>
+      </c>
+      <c r="D78" s="9">
+        <v>180</v>
+      </c>
+      <c r="E78" s="9">
+        <v>60</v>
+      </c>
+      <c r="F78" s="9">
+        <v>0</v>
+      </c>
+      <c r="G78" s="9">
+        <v>0</v>
+      </c>
+      <c r="H78" s="9">
+        <v>210</v>
+      </c>
+      <c r="I78" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="10" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J78" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="12"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+        <v>420</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N78" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>46320</v>
       </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="10" t="str">
+      <c r="B79" s="9">
+        <v>600</v>
+      </c>
+      <c r="C79" s="9">
+        <v>20</v>
+      </c>
+      <c r="D79" s="9">
+        <v>120</v>
+      </c>
+      <c r="E79" s="9">
+        <v>60</v>
+      </c>
+      <c r="F79" s="9">
+        <v>0</v>
+      </c>
+      <c r="G79" s="9">
+        <v>0</v>
+      </c>
+      <c r="H79" s="9">
+        <v>240</v>
+      </c>
+      <c r="I79" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J79" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
-      <c r="N79" s="12"/>
+        <v>400</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N79" s="12" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>46321</v>
       </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="10" t="str">
+      <c r="B80" s="9">
+        <v>540</v>
+      </c>
+      <c r="C80" s="9">
+        <v>30</v>
+      </c>
+      <c r="D80" s="9">
+        <v>180</v>
+      </c>
+      <c r="E80" s="9">
+        <v>45</v>
+      </c>
+      <c r="F80" s="9">
+        <v>0</v>
+      </c>
+      <c r="G80" s="9">
+        <v>0</v>
+      </c>
+      <c r="H80" s="9">
+        <v>210</v>
+      </c>
+      <c r="I80" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="10" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J80" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="11"/>
-      <c r="N80" s="12"/>
+        <v>435</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N80" s="12" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="8">

--- a/12608100.xlsx
+++ b/12608100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/178e7b8b65df52d4/Desktop/CAP-776/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="984" documentId="8_{423A2F30-43C3-4C4F-AB9B-22B4BC24882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B3AFDCA-0E72-47D4-ADDE-477B1BF45547}"/>
+  <xr:revisionPtr revIDLastSave="1026" documentId="8_{423A2F30-43C3-4C4F-AB9B-22B4BC24882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32ACF336-B8C7-47C4-B925-954B7FD9D6F4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="129">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -410,6 +410,18 @@
   </si>
   <si>
     <t>it's a holiday.</t>
+  </si>
+  <si>
+    <t>due to karwachauth, classes were only till 3:20 pm</t>
+  </si>
+  <si>
+    <t>ca of networking</t>
+  </si>
+  <si>
+    <t>ok ok</t>
+  </si>
+  <si>
+    <t>I don't want to go to class but still I have to</t>
   </si>
 </sst>
 </file>
@@ -4663,101 +4675,189 @@
         <v>124</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>46322</v>
       </c>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="10" t="str">
+      <c r="B81" s="9">
+        <v>480</v>
+      </c>
+      <c r="C81" s="9">
+        <v>30</v>
+      </c>
+      <c r="D81" s="9">
+        <v>210</v>
+      </c>
+      <c r="E81" s="9">
+        <v>30</v>
+      </c>
+      <c r="F81" s="9">
+        <v>350</v>
+      </c>
+      <c r="G81" s="9">
+        <v>7</v>
+      </c>
+      <c r="H81" s="9">
+        <v>180</v>
+      </c>
+      <c r="I81" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="10" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J81" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="11"/>
-      <c r="L81" s="11"/>
-      <c r="M81" s="11"/>
-      <c r="N81" s="12"/>
+        <v>160</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L81" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M81" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N81" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>46323</v>
       </c>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="10" t="str">
+      <c r="B82" s="9">
+        <v>480</v>
+      </c>
+      <c r="C82" s="9">
+        <v>25</v>
+      </c>
+      <c r="D82" s="9">
+        <v>180</v>
+      </c>
+      <c r="E82" s="9">
+        <v>45</v>
+      </c>
+      <c r="F82" s="9">
+        <v>200</v>
+      </c>
+      <c r="G82" s="9">
+        <v>4</v>
+      </c>
+      <c r="H82" s="9">
+        <v>210</v>
+      </c>
+      <c r="I82" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="10" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J82" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="11"/>
-      <c r="L82" s="11"/>
-      <c r="M82" s="11"/>
-      <c r="N82" s="12"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+      <c r="K82" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L82" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M82" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N82" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <v>46324</v>
       </c>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
-      <c r="I83" s="10" t="str">
+      <c r="B83" s="9">
+        <v>600</v>
+      </c>
+      <c r="C83" s="9">
+        <v>20</v>
+      </c>
+      <c r="D83" s="9">
+        <v>180</v>
+      </c>
+      <c r="E83" s="9">
+        <v>60</v>
+      </c>
+      <c r="F83" s="9">
+        <v>300</v>
+      </c>
+      <c r="G83" s="9">
+        <v>6</v>
+      </c>
+      <c r="H83" s="9">
+        <v>120</v>
+      </c>
+      <c r="I83" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="10" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J83" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="11"/>
-      <c r="L83" s="11"/>
-      <c r="M83" s="11"/>
-      <c r="N83" s="12"/>
+        <v>160</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L83" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M83" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N83" s="12" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>46325</v>
       </c>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="10" t="str">
+      <c r="B84" s="9">
+        <v>540</v>
+      </c>
+      <c r="C84" s="9">
+        <v>20</v>
+      </c>
+      <c r="D84" s="9">
+        <v>120</v>
+      </c>
+      <c r="E84" s="9">
+        <v>150</v>
+      </c>
+      <c r="F84" s="9">
+        <v>300</v>
+      </c>
+      <c r="G84" s="9">
+        <v>6</v>
+      </c>
+      <c r="H84" s="9">
+        <v>180</v>
+      </c>
+      <c r="I84" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="10" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J84" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K84" s="11"/>
-      <c r="L84" s="11"/>
-      <c r="M84" s="11"/>
-      <c r="N84" s="12"/>
+        <v>130</v>
+      </c>
+      <c r="K84" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L84" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M84" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N84" s="12" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
